--- a/Dezi Art Prize Student Data Scraping/master_students.xlsx
+++ b/Dezi Art Prize Student Data Scraping/master_students.xlsx
@@ -26,6 +26,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CCA" sheetId="17" state="visible" r:id="rId17"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MassArt" sheetId="18" state="visible" r:id="rId18"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="U Michigan Stamps" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CalArts" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UCLA" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columbia College Chicago" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'RIT'!$A$5:$I$326</definedName>
@@ -47,6 +50,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'CCA'!$A$5:$I$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'MassArt'!$A$5:$I$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'U Michigan Stamps'!$A$5:$I$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'CalArts'!$A$5:$I$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'UCLA'!$A$5:$I$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'Columbia College Chicago'!$A$5:$I$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -42546,6 +42552,3557 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Source: CalArts 'High Pass' BFA Class of 2026 group exhibition page (names only; site requires crawl4ai due to cookie-consent/Cloudflare Turnstile blocking a plain fetch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>URL: https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Accessed: 2026-08-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>graduation_year</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>portfolio_url</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>college</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>contacted</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Rita Aldridge</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Adrian Anguiano</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Elyse Beavers</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Raven Bridgewaters</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Jessica Yuexi Chen</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Indie Courtney</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Xochitl Quetzalli Cruz</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Sophie Darling</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ivan Nuñez DelaCruz</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Angharad Fitzgerald</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Jonathan Jin</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Amaris Jordan</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Riley Kate</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Sadira Kuelling</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Mackenzie Lord</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Eugenia Moreeva</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Ethan Nahman</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Mike Nott</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Elizaveta Novikova</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Okey Ofomata</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Natalee Park</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Suzy Park</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Abraham Perez</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Ella Rose</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Solomon Rosenthal</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Frances Sheehy</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Elliot Smolin</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Marisa del toro</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>QQ Yi</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A5:I34"/>
+  <dataValidations count="2">
+    <dataValidation sqref="G6:G34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H6:H34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"No response,Interested,Not interested,Bounced,Follow-up needed"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Source: UCLA Department of Art — current Graduate Students directory by area of study (Ceramics, Interdisciplinary Studio, New Genres, Painting and Drawing, Photography, Sculpture), each linking to a personal portfolio/Instagram where available</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>URL: https://www.art.ucla.edu/graduate-students</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Accessed: 2026-08-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>graduation_year</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>portfolio_url</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>college</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>contacted</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Dane Nakama</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>MFA Ceramics</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://www.bydanenakama.com/</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Ethan Shaw</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>MFA Ceramics</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/niceguysfinishinlast</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>g.aguilar magaña</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>MFA Ceramics</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://www.geneaguilarstudio.com/</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Lynsey Robertson</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>MFA Ceramics</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://www.lynseyjrobertson.com/</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Utē Petit</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>MFA Ceramics</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>No portfolio/social link listed for this student</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Victor Saucedo</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>MFA Ceramics</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>No portfolio/social link listed for this student</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Felix Li</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>MFA Interdisciplinary Studio</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>No portfolio/social link listed for this student</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Lucas Wrench</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>MFA Interdisciplinary Studio</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://www.lucaswrench.info</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Sabaah Folayan</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>MFA Interdisciplinary Studio</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://www.sabaah.is/</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Vanessa Norton</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>MFA Interdisciplinary Studio</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://www.vanessanorton.com/</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>vincent hernandez</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>MFA Interdisciplinary Studio</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>No portfolio/social link listed for this student</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Carlos Camacho</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>MFA New Genres</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>No portfolio/social link listed for this student</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Emir West</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>MFA New Genres</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>No portfolio/social link listed for this student</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Jazmin Jazzy Romero</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>MFA New Genres</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://www.jazminromero.com/</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Markele Cullins</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>MFA New Genres</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>https://markelecullins.com/</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Samar Al Summary</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>MFA New Genres</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://www.samaralsummary.com</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Anja Salonen</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>MFA Painting and Drawing</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/anjasalonen/</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Dilan Torres</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>MFA Painting and Drawing</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>No portfolio/social link listed for this student</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Gillian N Haigh</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>MFA Painting and Drawing</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://gilliannhaigh.com/</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Jacqueline Valenzuela</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>MFA Painting and Drawing</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>https://jacquelinevalenzuela.com/</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Jerry Alexis Peña</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>MFA Painting and Drawing</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jerryalexispena</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Luke Francis Austin</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>MFA Painting and Drawing</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/l.f.austin/</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Magnus Maxine Flowers</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>MFA Painting and Drawing</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>No portfolio/social link listed for this student</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Roshini Agarwal</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>MFA Painting and Drawing</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/roshini_agarwal</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Tammy Chang</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>MFA Painting and Drawing</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>https://www.tammy-chang.com/</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Victor Ballesteros</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>MFA Painting and Drawing</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>http://instagram.com/vmballesterosg</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Wihro Kim</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>MFA Painting and Drawing</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>No portfolio/social link listed for this student</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Alina van Ryzin</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>MFA Photography</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/alinavanryzin</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Andrés de Varona</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>MFA Photography</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://www.andresmario.com/</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Anne Vetter</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>MFA Photography</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>https://www.acvetter.com/</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Ashley Michelle Hannah</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>MFA Photography</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>https://ashleymichellehannah.com/</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Keegan Isaac Holden</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>MFA Photography</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://www.keeganholden.com/</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>abhishek kulkarni</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>MFA Sculpture</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/a.ar.kay/</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Andrew Sungtaek</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>MFA Sculpture</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/a.sungtaek</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Aryana Polat</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>MFA Sculpture</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>https://aryanapolat.com/</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>libbi ponce</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>MFA Sculpture</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>https://libbiponce.com/</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>tunmi da silva</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>MFA Sculpture</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>https://www.tunmidasilva.com/</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Yao Wang</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>MFA Sculpture</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://wangyao.info/</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A5:I43"/>
+  <dataValidations count="2">
+    <dataValidation sqref="G6:G43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H6:H43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"No response,Interested,Not interested,Bounced,Follow-up needed"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Source: Columbia College Chicago — 'Human Condition' 2026 BA/BFA Fine Art Exhibition page, Hokin Gallery and C33 Gallery exhibitor lists (names only). Note: 2 of 24 names have unusual letter-spacing in the source HTML itself (e.g. 'Faith H o g a n') — kept verbatim, flagged in notes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>URL: https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Accessed: 2026-08-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>graduation_year</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>portfolio_url</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>college</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>contacted</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Jupiter Brodie</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BFA/BA Fine Art (Hokin Gallery)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Columbia College Chicago</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Name only, from 'Hokin Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Carley Brown</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BFA/BA Fine Art (Hokin Gallery)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Columbia College Chicago</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Name only, from 'Hokin Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Fiona Connors</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BFA/BA Fine Art (Hokin Gallery)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Columbia College Chicago</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Name only, from 'Hokin Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Jocelyn Diaz</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BFA/BA Fine Art (Hokin Gallery)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Columbia College Chicago</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Name only, from 'Hokin Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Faith H o g a n</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BFA/BA Fine Art (Hokin Gallery)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Columbia College Chicago</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Name only, from 'Hokin Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published; NOTE: name appears to have unusual letter-spacing in the source HTML itself (e.g. single letters separated by spaces) — kept verbatim, may not reflect the person's actual name spelling</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Emelia Kay</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BFA/BA Fine Art (Hokin Gallery)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Columbia College Chicago</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Name only, from 'Hokin Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Aja "Morningstar" Martin</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BFA/BA Fine Art (Hokin Gallery)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Columbia College Chicago</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Name only, from 'Hokin Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Hai Martinez</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BFA/BA Fine Art (Hokin Gallery)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Columbia College Chicago</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Name only, from 'Hokin Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Frida Mejia</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>BFA/BA Fine Art (Hokin Gallery)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Columbia College Chicago</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Name only, from 'Hokin Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Nat Slavin</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BFA/BA Fine Art (Hokin Gallery)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Columbia College Chicago</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Name only, from 'Hokin Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Brianna Wilkins</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BFA/BA Fine Art (Hokin Gallery)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Columbia College Chicago</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Name only, from 'Hokin Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Isa Woodard</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BFA/BA Fine Art (Hokin Gallery)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Columbia College Chicago</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Name only, from 'Hokin Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Liz Z e r m e n o Robles</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BFA/BA Fine Art (Hokin Gallery)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Columbia College Chicago</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Name only, from 'Hokin Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published; NOTE: name appears to have unusual letter-spacing in the source HTML itself (e.g. single letters separated by spaces) — kept verbatim, may not reflect the person's actual name spelling</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Jala Bowers</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BFA/BA Fine Art (C33 Gallery)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Columbia College Chicago</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Name only, from 'C33 Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Jenna Davis</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BFA/BA Fine Art (C33 Gallery)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Columbia College Chicago</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Name only, from 'C33 Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Trevell Hampton</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>BFA/BA Fine Art (C33 Gallery)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Columbia College Chicago</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Name only, from 'C33 Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Alivia King</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>BFA/BA Fine Art (C33 Gallery)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Columbia College Chicago</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Name only, from 'C33 Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ana Lara</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>BFA/BA Fine Art (C33 Gallery)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Columbia College Chicago</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Name only, from 'C33 Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Drew Malapanes</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>BFA/BA Fine Art (C33 Gallery)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Columbia College Chicago</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Name only, from 'C33 Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Elise N e a l</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>BFA/BA Fine Art (C33 Gallery)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Columbia College Chicago</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Name only, from 'C33 Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published; NOTE: name appears to have unusual letter-spacing in the source HTML itself (e.g. single letters separated by spaces) — kept verbatim, may not reflect the person's actual name spelling</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Wang Jing Yi (Eliana Pinkert)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>BFA/BA Fine Art (C33 Gallery)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Columbia College Chicago</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Name only, from 'C33 Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Cristian Romero</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>BFA/BA Fine Art (C33 Gallery)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Columbia College Chicago</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Name only, from 'C33 Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Liza Smith</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>BFA/BA Fine Art (C33 Gallery)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Columbia College Chicago</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Name only, from 'C33 Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Stefanie Valle Aguilera</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>BFA/BA Fine Art (C33 Gallery)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Columbia College Chicago</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Name only, from 'C33 Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A5:I29"/>
+  <dataValidations count="2">
+    <dataValidation sqref="G6:G29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H6:H29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"No response,Interested,Not interested,Bounced,Follow-up needed"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Dezi Art Prize Student Data Scraping/master_students.xlsx
+++ b/Dezi Art Prize Student Data Scraping/master_students.xlsx
@@ -29,6 +29,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CalArts" sheetId="20" state="visible" r:id="rId20"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UCLA" sheetId="21" state="visible" r:id="rId21"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columbia College Chicago" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Iowa" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UW Art" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BGSU" sheetId="25" state="visible" r:id="rId25"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'RIT'!$A$5:$I$326</definedName>
@@ -53,6 +56,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'CalArts'!$A$5:$I$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'UCLA'!$A$5:$I$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'Columbia College Chicago'!$A$5:$I$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'Iowa'!$A$5:$I$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'UW Art'!$A$5:$I$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'BGSU'!$A$5:$I$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -46103,6 +46109,1638 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Source: University of Iowa School of Art, Art History, and Design — MFA Virtual Exhibitions page (2024-2026 cohorts), each linking to a Matterport 3D exhibition tour rather than a personal portfolio site</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>URL: https://art.uiowa.edu/events/mfa-virtual-exhibitions</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Accessed: 2026-08-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>graduation_year</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>portfolio_url</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>college</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>contacted</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Heather Steckler</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>MFA Printmaking</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://my.matterport.com/show/?m=bUQuRPrPXn5</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>University of Iowa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Portfolio URL is a Matterport 3D virtual exhibition tour, not a personal site; no email published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Cara Krippner</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>MFA Painting and Drawing</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://my.matterport.com/show/?m=QMBBNq3N6VX</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>University of Iowa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Portfolio URL is a Matterport 3D virtual exhibition tour, not a personal site; no email published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Anna Roemerman</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>MFA 3D Design</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://my.matterport.com/show/?m=1RzXZaJURgK</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>University of Iowa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Portfolio URL is a Matterport 3D virtual exhibition tour, not a personal site; no email published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Antonia Baafi</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>MFA Jewelry and Metal Arts</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://my.matterport.com/show/?m=E4APuduuJ7R</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>University of Iowa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Portfolio URL is a Matterport 3D virtual exhibition tour, not a personal site; no email published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Lya Finston</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>MFA Printmaking</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://my.matterport.com/show/?m=PkmkecLPwnV</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>University of Iowa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Portfolio URL is a Matterport 3D virtual exhibition tour, not a personal site; no email published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Amanda Shepard</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>MFA Jewelry and Metal Arts</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://my.matterport.com/show/?m=uCPoUCvVax8</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>University of Iowa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Portfolio URL is a Matterport 3D virtual exhibition tour, not a personal site; no email published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ben Eastman</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>MFA 3D Design</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://my.matterport.com/show/?m=1ncCV6yM24a</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>University of Iowa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Portfolio URL is a Matterport 3D virtual exhibition tour, not a personal site; no email published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Javier Espinosa Momox</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>MFA Ceramics</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://my.matterport.com/show/?m=gAnFZ1qj4mX</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>University of Iowa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Portfolio URL is a Matterport 3D virtual exhibition tour, not a personal site; no email published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Patrick Ryan</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>MFA Ceramics</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://my.matterport.com/show/?m=e6BTTHxyJVm</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>University of Iowa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Portfolio URL is a Matterport 3D virtual exhibition tour, not a personal site; no email published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Al-Qawi Nanavati</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>MFA Printmaking</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://my.matterport.com/show/?m=ZLZKMucHd3u</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>University of Iowa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Portfolio URL is a Matterport 3D virtual exhibition tour, not a personal site; no email published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Gracie Baer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>MFA Sculpture &amp; Intermedia</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://my.matterport.com/show/?m=59w5kkDgyys</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>University of Iowa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Portfolio URL is a Matterport 3D virtual exhibition tour, not a personal site; no email published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Braden Dexter</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>MFA Graphic Design</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://my.matterport.com/show/?m=c5LN5QkVjdo</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>University of Iowa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Portfolio URL is a Matterport 3D virtual exhibition tour, not a personal site; no email published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Agnes Harry Mills</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>MFA Jewlery and Metal Arts</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://my.matterport.com/show/?m=vccXRs9sB2o</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>University of Iowa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Portfolio URL is a Matterport 3D virtual exhibition tour, not a personal site; no email published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Kyle Agnew</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>MFA Photography</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://my.matterport.com/show/?m=3veaLSxJd3y</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>University of Iowa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Portfolio URL is a Matterport 3D virtual exhibition tour, not a personal site; no email published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Sofia Echeverri</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>MFA Painting and Drawing</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>https://my.matterport.com/show/?m=L2tVk5UcqYH</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>University of Iowa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Portfolio URL is a Matterport 3D virtual exhibition tour, not a personal site; no email published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Na'ah Gordon</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>MFA Painting and Drawing</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://my.matterport.com/show/?m=8mfrTxRfsF9</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>University of Iowa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Portfolio URL is a Matterport 3D virtual exhibition tour, not a personal site; no email published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Jordan Ramsey Ismaiel</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>MFA Painting and Drawing</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://my.matterport.com/show/?m=Gt8PNGatZUC</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>University of Iowa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Portfolio URL is a Matterport 3D virtual exhibition tour, not a personal site; no email published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Lauren Krukowski</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>MFA Printmaking</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://my.matterport.com/show/?m=MbXETFgfm4h</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>University of Iowa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Portfolio URL is a Matterport 3D virtual exhibition tour, not a personal site; no email published on source page</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A5:I23"/>
+  <dataValidations count="2">
+    <dataValidation sqref="G6:G23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H6:H23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"No response,Interested,Not interested,Bounced,Follow-up needed"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Source: University of Washington 2026 MFA + MDes Thesis Exhibition page (Henry Art Gallery) — names only; source does not map a specific discipline to each individual student</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>URL: https://henryart.org/exhibitions/2026-university-of-washington-mfa-mdes-thesis-exhibition</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Accessed: 2026-08-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>graduation_year</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>portfolio_url</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>college</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>contacted</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Stephanie Alacon</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>MFA/MDes (UW Art — discipline not specified per student)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://henryart.org/exhibitions/2026-university-of-washington-mfa-mdes-thesis-exhibition</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>University of Washington</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Name only, from Henry Art Gallery thesis exhibition page; no email/portfolio published; source page does not map a specific discipline to each individual student</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Dahae Cheon</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>MFA/MDes (UW Art — discipline not specified per student)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://henryart.org/exhibitions/2026-university-of-washington-mfa-mdes-thesis-exhibition</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>University of Washington</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Name only, from Henry Art Gallery thesis exhibition page; no email/portfolio published; source page does not map a specific discipline to each individual student</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Li-Yuan Chiou</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>MFA/MDes (UW Art — discipline not specified per student)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://henryart.org/exhibitions/2026-university-of-washington-mfa-mdes-thesis-exhibition</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>University of Washington</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Name only, from Henry Art Gallery thesis exhibition page; no email/portfolio published; source page does not map a specific discipline to each individual student</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Jeff Jiang</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>MFA/MDes (UW Art — discipline not specified per student)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://henryart.org/exhibitions/2026-university-of-washington-mfa-mdes-thesis-exhibition</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>University of Washington</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Name only, from Henry Art Gallery thesis exhibition page; no email/portfolio published; source page does not map a specific discipline to each individual student</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Victoria Mackender</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>MFA/MDes (UW Art — discipline not specified per student)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://henryart.org/exhibitions/2026-university-of-washington-mfa-mdes-thesis-exhibition</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>University of Washington</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Name only, from Henry Art Gallery thesis exhibition page; no email/portfolio published; source page does not map a specific discipline to each individual student</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Alex Moni-Sauri</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>MFA/MDes (UW Art — discipline not specified per student)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://henryart.org/exhibitions/2026-university-of-washington-mfa-mdes-thesis-exhibition</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>University of Washington</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Name only, from Henry Art Gallery thesis exhibition page; no email/portfolio published; source page does not map a specific discipline to each individual student</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Oscar Pearson</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>MFA/MDes (UW Art — discipline not specified per student)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://henryart.org/exhibitions/2026-university-of-washington-mfa-mdes-thesis-exhibition</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>University of Washington</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Name only, from Henry Art Gallery thesis exhibition page; no email/portfolio published; source page does not map a specific discipline to each individual student</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chave Pichardo</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>MFA/MDes (UW Art — discipline not specified per student)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://henryart.org/exhibitions/2026-university-of-washington-mfa-mdes-thesis-exhibition</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>University of Washington</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Name only, from Henry Art Gallery thesis exhibition page; no email/portfolio published; source page does not map a specific discipline to each individual student</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Andrew Roibal</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>MFA/MDes (UW Art — discipline not specified per student)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://henryart.org/exhibitions/2026-university-of-washington-mfa-mdes-thesis-exhibition</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>University of Washington</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Name only, from Henry Art Gallery thesis exhibition page; no email/portfolio published; source page does not map a specific discipline to each individual student</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Ryan Walters</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>MFA/MDes (UW Art — discipline not specified per student)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://henryart.org/exhibitions/2026-university-of-washington-mfa-mdes-thesis-exhibition</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>University of Washington</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Name only, from Henry Art Gallery thesis exhibition page; no email/portfolio published; source page does not map a specific discipline to each individual student</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A5:I15"/>
+  <dataValidations count="2">
+    <dataValidation sqref="G6:G15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H6:H15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"No response,Interested,Not interested,Bounced,Follow-up needed"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Source: BGSU ScholarWorks — School of Art MA and MFA Graduate Exhibitions, Portfolios, and Theses repository, 2025 cohort (thesis title + author name; portfolio_url is the repository record, not a personal site)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>URL: https://scholarworks.bgsu.edu/ms_art/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Accessed: 2026-08-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>graduation_year</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>portfolio_url</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>college</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>contacted</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Syed Fatmi</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>MFA Studio Art</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://scholarworks.bgsu.edu/ms_art/542</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>BGSU</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Thesis title: "OMNISYS"; no email/personal portfolio published on source page (portfolio_url is the ScholarWorks repository record)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Nick Felaris</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>MFA Studio Art</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://scholarworks.bgsu.edu/ms_art/543</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>BGSU</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Thesis title: "Nick Felaris Master of Fine Arts"; no email/personal portfolio published on source page (portfolio_url is the ScholarWorks repository record)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Precious Gyekye</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>MFA Studio Art</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://scholarworks.bgsu.edu/ms_art/544</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>BGSU</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Thesis title: "Unraveling Silence"; no email/personal portfolio published on source page (portfolio_url is the ScholarWorks repository record)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Peter Kiladejo</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>MFA Studio Art</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://scholarworks.bgsu.edu/ms_art/545</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>BGSU</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Thesis title: "Adetope Peter Kiladejo Master of Fine Arts"; no email/personal portfolio published on source page (portfolio_url is the ScholarWorks repository record)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Rachel Krieger</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>MFA Studio Art</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://scholarworks.bgsu.edu/ms_art/546</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>BGSU</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Thesis title: "Rachel Krieger"; no email/personal portfolio published on source page (portfolio_url is the ScholarWorks repository record)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Kamrun Mim</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>MFA Studio Art</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://scholarworks.bgsu.edu/ms_art/547</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>BGSU</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Thesis title: "Kamrun Mim"; no email/personal portfolio published on source page (portfolio_url is the ScholarWorks repository record)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A5:I11"/>
+  <dataValidations count="2">
+    <dataValidation sqref="G6:G11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H6:H11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"No response,Interested,Not interested,Bounced,Follow-up needed"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Dezi Art Prize Student Data Scraping/master_students.xlsx
+++ b/Dezi Art Prize Student Data Scraping/master_students.xlsx
@@ -47499,7 +47499,11 @@
           <t>Syed Fatmi</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>syedway.digital@gmail.com</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>MFA Studio Art</t>
@@ -47512,7 +47516,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://scholarworks.bgsu.edu/ms_art/542</t>
+          <t>https://syedway.com/</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -47528,7 +47532,7 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Thesis title: "OMNISYS"; no email/personal portfolio published on source page (portfolio_url is the ScholarWorks repository record)</t>
+          <t>Thesis title: "OMNISYS"; email and portfolio found via web search (personal site syedway.com, confirmed via matching thesis title/LinkedIn)</t>
         </is>
       </c>
     </row>
@@ -47707,7 +47711,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://scholarworks.bgsu.edu/ms_art/547</t>
+          <t>https://kamrunnahermim.com/</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -47723,7 +47727,7 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Thesis title: "Kamrun Mim"; no email/personal portfolio published on source page (portfolio_url is the ScholarWorks repository record)</t>
+          <t>Thesis title: "Kamrun Mim"; personal site found via web search (kamrunnahermim.com) but returned HTTP 403 on fetch — could not retrieve email; try visiting contact page manually</t>
         </is>
       </c>
     </row>

--- a/Dezi Art Prize Student Data Scraping/master_students.xlsx
+++ b/Dezi Art Prize Student Data Scraping/master_students.xlsx
@@ -47542,7 +47542,11 @@
           <t>Nick Felaris</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>nickfelaris@hotmail.com</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>MFA Studio Art</t>
@@ -47571,7 +47575,7 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Thesis title: "Nick Felaris Master of Fine Arts"; no email/personal portfolio published on source page (portfolio_url is the ScholarWorks repository record)</t>
+          <t>Thesis title: "Nick Felaris Master of Fine Arts"; email confirmed by user</t>
         </is>
       </c>
     </row>
@@ -47659,7 +47663,11 @@
           <t>Rachel Krieger</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>rachelle@rachellekrieger.com</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
           <t>MFA Studio Art</t>
@@ -47672,7 +47680,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://scholarworks.bgsu.edu/ms_art/546</t>
+          <t>https://www.rachellekrieger.com/</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -47688,7 +47696,7 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Thesis title: "Rachel Krieger"; no email/personal portfolio published on source page (portfolio_url is the ScholarWorks repository record)</t>
+          <t>Thesis title: "Rachel Krieger"; email and portfolio confirmed by user via rachellekrieger.com contact page</t>
         </is>
       </c>
     </row>
@@ -47698,7 +47706,11 @@
           <t>Kamrun Mim</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>kamrunmim.print@gmail.com</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
           <t>MFA Studio Art</t>
@@ -47711,7 +47723,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://kamrunnahermim.com/</t>
+          <t>https://kamrunnahermim.wordpress.com/</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -47727,7 +47739,7 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Thesis title: "Kamrun Mim"; personal site found via web search (kamrunnahermim.com) but returned HTTP 403 on fetch — could not retrieve email; try visiting contact page manually</t>
+          <t>Thesis title: "Kamrun Mim"; email and portfolio confirmed by user via kamrunnahermim.wordpress.com/about (bio/CV section)</t>
         </is>
       </c>
     </row>

--- a/Dezi Art Prize Student Data Scraping/master_students.xlsx
+++ b/Dezi Art Prize Student Data Scraping/master_students.xlsx
@@ -47137,7 +47137,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://henryart.org/exhibitions/2026-university-of-washington-mfa-mdes-thesis-exhibition</t>
+          <t>https://jeff-jiang.com/</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -47153,7 +47153,7 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Name only, from Henry Art Gallery thesis exhibition page; no email/portfolio published; source page does not map a specific discipline to each individual student</t>
+          <t>Personal site found via web search (jeff-jiang.com, footwear/product design background) but no email visible in static HTML — likely a JS-rendered contact form; no email found</t>
         </is>
       </c>
     </row>
@@ -47176,7 +47176,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://henryart.org/exhibitions/2026-university-of-washington-mfa-mdes-thesis-exhibition</t>
+          <t>https://www.vamack.com/</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -47192,7 +47192,7 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Name only, from Henry Art Gallery thesis exhibition page; no email/portfolio published; source page does not map a specific discipline to each individual student</t>
+          <t>Personal site found via web search (vamack.com) but this tool's fetcher could not resolve the domain (DNS failure) — try visiting manually for contact info; also has Instagram @vamackender</t>
         </is>
       </c>
     </row>
@@ -47254,7 +47254,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://henryart.org/exhibitions/2026-university-of-washington-mfa-mdes-thesis-exhibition</t>
+          <t>https://oscarpearsonart.wixsite.com/studio</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -47270,7 +47270,7 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Name only, from Henry Art Gallery thesis exhibition page; no email/portfolio published; source page does not map a specific discipline to each individual student</t>
+          <t>Personal site found via web search (Wix site, Instagram @oscarpearson_) but no email visible — only a Wix contact form; no email found. NOTE: a different, unrelated Oscar Pearson (California muralist/gallery artist) also shows up in search — not to be confused with this student</t>
         </is>
       </c>
     </row>
@@ -47371,7 +47371,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://henryart.org/exhibitions/2026-university-of-washington-mfa-mdes-thesis-exhibition</t>
+          <t>https://www.ryanwalters.art/</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -47387,7 +47387,7 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Name only, from Henry Art Gallery thesis exhibition page; no email/portfolio published; source page does not map a specific discipline to each individual student</t>
+          <t>Personal site found via web search (ryanwalters.art) but this tool's fetcher could not resolve the .art domain (DNS failure) — try visiting manually for contact info</t>
         </is>
       </c>
     </row>

--- a/Dezi Art Prize Student Data Scraping/master_students.xlsx
+++ b/Dezi Art Prize Student Data Scraping/master_students.xlsx
@@ -31338,7 +31338,11 @@
           <t>Olivia Greenberg</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>oliviadylan129@gmail.com</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>MFA Photography</t>
@@ -31351,7 +31355,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://calendar.massart.edu/event/2026-mfa-thesis-exhibition-PARTI</t>
+          <t>https://www.oliviadylanphotography.com/</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -31367,7 +31371,7 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Name only, from 'FEATURED ARTISTS' list; no email/portfolio published on source page</t>
+          <t>Email and portfolio found via web search (own site oliviadylanphotography.com contact page)</t>
         </is>
       </c>
     </row>
@@ -31377,7 +31381,11 @@
           <t>Anastasia Sierra</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>info@anastasiasierra.com</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>MFA Photography</t>
@@ -31390,7 +31398,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://calendar.massart.edu/event/2026-mfa-thesis-exhibition-PARTI</t>
+          <t>https://www.anastasiasierra.com/</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -31406,7 +31414,7 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Name only, from 'FEATURED ARTISTS' list; no email/portfolio published on source page</t>
+          <t>Email and portfolio found via web search (own site anastasiasierra.com/about)</t>
         </is>
       </c>
     </row>
@@ -31429,7 +31437,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://calendar.massart.edu/event/2026-mfa-thesis-exhibition-PARTI</t>
+          <t>https://visura.co/lspencer/about</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -31445,7 +31453,7 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Name only, from 'FEATURED ARTISTS' list; no email/portfolio published on source page</t>
+          <t>Photographer/writer based in Winchester, MA; Visura profile found via web search but returned HTTP 403 on fetch — no email found</t>
         </is>
       </c>
     </row>
@@ -31455,7 +31463,11 @@
           <t>Shailee Thakkar</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>shailee.v.thakkar@gmail.com</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
           <t>MFA Studio Arts</t>
@@ -31468,7 +31480,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://calendar.massart.edu/event/2026-mfa-thesis-exhibition-PARTI</t>
+          <t>https://www.shaileethakkar.com/</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -31484,7 +31496,7 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Name only, from 'FEATURED ARTISTS' list; no email/portfolio published on source page</t>
+          <t>Email and portfolio found via web search (own site shaileethakkar.com/aboutme footer)</t>
         </is>
       </c>
     </row>
@@ -31533,7 +31545,11 @@
           <t>Antonio Bailey</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>antoniobaileylocal@gmail.com</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr">
         <is>
           <t>MFA Photography</t>
@@ -31546,7 +31562,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://calendar.massart.edu/event/2026-spring-mfa-thesis-exhibition-part-ii</t>
+          <t>https://www.antoniobailey.com/</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -31562,7 +31578,7 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Name only, from 'FEATURED ARTISTS' list; no email/portfolio published on source page</t>
+          <t>Email and portfolio found via web search (own site antoniobailey.com/about)</t>
         </is>
       </c>
     </row>
@@ -31585,7 +31601,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://calendar.massart.edu/event/2026-spring-mfa-thesis-exhibition-part-ii</t>
+          <t>https://camrynconnolly.com/</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -31601,7 +31617,7 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Name only, from 'FEATURED ARTISTS' list; no email/portfolio published on source page</t>
+          <t>Personal site found via web search (camrynconnolly.com) but only a contact form is shown, no visible email; Instagram @camrynscollections</t>
         </is>
       </c>
     </row>
@@ -31624,7 +31640,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://calendar.massart.edu/event/2026-spring-mfa-thesis-exhibition-part-ii</t>
+          <t>https://www.suzigrossman.com/</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -31640,7 +31656,7 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Name only, from 'FEATURED ARTISTS' list; no email/portfolio published on source page</t>
+          <t>UNVERIFIED possible email: Suzi@suzigrossman.com — surfaced via web search summary of the site's contact page, but the email is JS-obfuscated on the live page and could not be independently confirmed by direct fetch; not written as confirmed</t>
         </is>
       </c>
     </row>

--- a/Dezi Art Prize Student Data Scraping/master_students.xlsx
+++ b/Dezi Art Prize Student Data Scraping/master_students.xlsx
@@ -13205,7 +13205,11 @@
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>No email found — Behance profile has no listed contact info, no personal site found</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13271,7 +13275,11 @@
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Own site returned HTTP 503 (site appears down) on repeated fetch attempts; CMU directory page has no direct email listed — try visiting waltersmits.com manually</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13337,7 +13345,11 @@
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Own site (yiyingwang666.com) could not be resolved by this tool's fetcher (DNS failure) — try visiting manually; CMU directory page has no direct email listed</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13380,7 +13392,11 @@
           <t>Amber N. Ford</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>studio@ambernford.com</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr">
         <is>
           <t>MFA Studio Art (First-Year MFA)</t>
@@ -13389,7 +13405,7 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://art.cmu.edu/people/amber-ford/</t>
+          <t>https://www.ambernford.com/</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -13403,7 +13419,11 @@
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Email and portfolio found via web search (own site ambernford.com/info)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -13446,7 +13466,11 @@
           <t>Sarah Al-Sarraj</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>info.sarahalsarraj@gmail.com</t>
+        </is>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
           <t>MFA Studio Art (First-Year MFA)</t>
@@ -13469,7 +13493,11 @@
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Email found via web search (own site sarahalsarraj.com)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -13617,7 +13645,11 @@
           <t>Stefanie Zito</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>info@stefaniezito.com</t>
+        </is>
+      </c>
       <c r="C19" t="inlineStr">
         <is>
           <t>MFA Studio Art (First-Year MFA)</t>
@@ -13640,7 +13672,11 @@
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Email found via web search (own site stefaniezito.com, listed as 'info[at]stefaniezito.com' anti-scrape format)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A5:I19"/>

--- a/Dezi Art Prize Student Data Scraping/master_students.xlsx
+++ b/Dezi Art Prize Student Data Scraping/master_students.xlsx
@@ -68071,10 +68071,14 @@
           <t>Charles Jarboe</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>charles.jarboe@gmail.com</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MFA Fine Arts</t>
+          <t>MFA Glass</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -68082,7 +68086,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://www.charles-jarboe.com/</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>Temple/Tyler</t>
@@ -68096,7 +68104,7 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: February 26 - March 1); no email/major/portfolio published on source page</t>
+          <t>Email and portfolio found via web search (own site charles-jarboe.com/bio)</t>
         </is>
       </c>
     </row>
@@ -68109,7 +68117,7 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MFA Fine Arts</t>
+          <t>MFA Photography</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -68131,7 +68139,7 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: February 26 - March 1); no email/major/portfolio published on source page</t>
+          <t>No email found via web search — no personal site surfaced</t>
         </is>
       </c>
     </row>
@@ -68166,7 +68174,7 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: February 26 - March 1); no email/major/portfolio published on source page</t>
+          <t>No email found via web search — no personal site surfaced</t>
         </is>
       </c>
     </row>
@@ -68176,10 +68184,14 @@
           <t>Amanda Crain-Freeland</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>amandancrain@gmail.com</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MFA Fine Arts</t>
+          <t>MFA Sculpture</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -68187,7 +68199,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://www.amandacrainfreeland.com/</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>Temple/Tyler</t>
@@ -68201,7 +68217,7 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: March 12-March 15); no email/major/portfolio published on source page</t>
+          <t>Email and portfolio found via web search (own site amandacrainfreeland.com CV page)</t>
         </is>
       </c>
     </row>
@@ -68214,7 +68230,7 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MFA Fine Arts</t>
+          <t>MFA Sculpture</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -68222,7 +68238,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://fernandanunez.com/</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>Temple/Tyler</t>
@@ -68236,7 +68256,7 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: March 12-March 15); no email/major/portfolio published on source page</t>
+          <t>Own site (fernandanunez.com) found via web search but returned HTTP 503 on fetch — try visiting manually</t>
         </is>
       </c>
     </row>
@@ -68249,7 +68269,7 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MFA Fine Arts</t>
+          <t>MFA Fiber/Sculpture</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -68257,7 +68277,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://www.mikaobayashi.com/</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>Temple/Tyler</t>
@@ -68271,7 +68295,7 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: March 12-March 15); no email/major/portfolio published on source page</t>
+          <t>Personal site found via web search (mikaobayashi.com) but no email visible — only Instagram and a /contact link; no email found</t>
         </is>
       </c>
     </row>
@@ -68284,7 +68308,7 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MFA Fine Arts</t>
+          <t>MFA Painting</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -68306,7 +68330,7 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: March 12-March 15); no email/major/portfolio published on source page</t>
+          <t>No email found via web search — no personal site surfaced</t>
         </is>
       </c>
     </row>
@@ -68319,7 +68343,7 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MFA Fine Arts</t>
+          <t>MFA Photography</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -68327,7 +68351,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://sophiadellarciprete.com/</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>Temple/Tyler</t>
@@ -68341,7 +68369,7 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: March 19 - March 22); no email/major/portfolio published on source page</t>
+          <t>Personal site found via web search (sophiadellarciprete.com) but no email visible in static HTML; no email found</t>
         </is>
       </c>
     </row>
@@ -68351,10 +68379,14 @@
           <t>Rae Helms</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Raehelmsprint@gmail.com</t>
+        </is>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MFA Fine Arts</t>
+          <t>MFA Printmaking</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -68362,7 +68394,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://raehelms.ink/</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>Temple/Tyler</t>
@@ -68376,7 +68412,7 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: March 19 - March 22); no email/major/portfolio published on source page</t>
+          <t>Email and portfolio found via web search (own site raehelms.ink)</t>
         </is>
       </c>
     </row>
@@ -68386,10 +68422,14 @@
           <t>Francesca Lally</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>francescalally@gmail.com</t>
+        </is>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MFA Fine Arts</t>
+          <t>MFA Printmaking</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -68397,7 +68437,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://www.francescalally.net/</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>Temple/Tyler</t>
@@ -68411,7 +68455,7 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: March 19 - March 22); no email/major/portfolio published on source page</t>
+          <t>Email and portfolio found via web search (own site francescalally.net/ccvv)</t>
         </is>
       </c>
     </row>
@@ -68424,7 +68468,7 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MFA Fine Arts</t>
+          <t>MFA Ceramics</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -68432,7 +68476,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://arizuaro.com/</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>Temple/Tyler</t>
@@ -68446,7 +68494,7 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: March 19 - March 22); no email/major/portfolio published on source page</t>
+          <t>Personal site found via web search (arizuaro.com) but no email visible — only Instagram link; no email found</t>
         </is>
       </c>
     </row>
@@ -68456,10 +68504,14 @@
           <t>Lilly Buttitta</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>lbuttittaart@gmail.com</t>
+        </is>
+      </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MFA Fine Arts</t>
+          <t>MFA Painting</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -68467,7 +68519,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://lillybuttitta.com/</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>Temple/Tyler</t>
@@ -68481,7 +68537,7 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: March 26- March 29); no email/major/portfolio published on source page</t>
+          <t>Email and portfolio found via web search (own site lillybuttitta.com)</t>
         </is>
       </c>
     </row>
@@ -68494,7 +68550,7 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MFA Fine Arts</t>
+          <t>MFA Painting</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -68516,7 +68572,7 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: March 26- March 29); no email/major/portfolio published on source page</t>
+          <t>No email found via web search — no personal site surfaced, only a LinkedIn profile</t>
         </is>
       </c>
     </row>
@@ -68551,7 +68607,7 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: March 26- March 29); no email/major/portfolio published on source page</t>
+          <t>No email found via web search — no personal site surfaced</t>
         </is>
       </c>
     </row>
@@ -68586,7 +68642,7 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: March 26- March 29); no email/major/portfolio published on source page</t>
+          <t>No email found via web search — no personal site surfaced</t>
         </is>
       </c>
     </row>
@@ -68621,7 +68677,7 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: April 2 - April 5); no email/major/portfolio published on source page</t>
+          <t>No email found via web search — no personal site surfaced</t>
         </is>
       </c>
     </row>
@@ -68634,7 +68690,7 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MFA Fine Arts</t>
+          <t>MFA Fiber and Material Studies</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -68642,7 +68698,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://maedehmehdipour.com/</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>Temple/Tyler</t>
@@ -68656,7 +68716,7 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: April 2 - April 5); no email/major/portfolio published on source page</t>
+          <t>Personal site found via web search (maedehmehdipour.com) but returned HTTP 403 on fetch — could not retrieve email; try visiting manually</t>
         </is>
       </c>
     </row>
@@ -68669,7 +68729,7 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MFA Fine Arts</t>
+          <t>MFA Printmaking</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -68691,7 +68751,7 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: April 2 - April 5); no email/major/portfolio published on source page</t>
+          <t>No email found via web search — only a LinkedIn profile surfaced, no personal site</t>
         </is>
       </c>
     </row>
@@ -68726,7 +68786,7 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: April 2 - April 5); no email/major/portfolio published on source page</t>
+          <t>No email found via web search — no personal site surfaced</t>
         </is>
       </c>
     </row>
@@ -68761,7 +68821,7 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: April 9 - April 12); no email/major/portfolio published on source page</t>
+          <t>No email found via web search — no personal site surfaced</t>
         </is>
       </c>
     </row>
@@ -68796,7 +68856,7 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: April 9 - April 12); no email/major/portfolio published on source page</t>
+          <t>No email found via web search — no personal site surfaced</t>
         </is>
       </c>
     </row>
@@ -68831,7 +68891,7 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: April 9 - April 12); no email/major/portfolio published on source page</t>
+          <t>No email found via web search — no personal site surfaced</t>
         </is>
       </c>
     </row>
@@ -68852,7 +68912,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>https://www.bensoloart.com/</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>Temple/Tyler</t>
@@ -68866,7 +68930,7 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: April 9 - April 12); no email/major/portfolio published on source page</t>
+          <t>Own site (bensoloart.com) found via web search but could not be resolved by this tool's fetcher (DNS failure) — try visiting manually</t>
         </is>
       </c>
     </row>
@@ -68887,7 +68951,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>https://scoby.page/log3y-logan-crompton</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
           <t>Temple/Tyler</t>
@@ -68901,7 +68969,7 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: April 16- April 19); no email/major/portfolio published on source page</t>
+          <t>Link-in-bio page (scoby.page) found via web search — not fetched for email this pass</t>
         </is>
       </c>
     </row>
@@ -68936,7 +69004,7 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: April 16- April 19); no email/major/portfolio published on source page</t>
+          <t>No email found via web search — no personal site surfaced (full name may be 'Boi Boy Cottrell' per one source)</t>
         </is>
       </c>
     </row>
@@ -68949,7 +69017,7 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MFA Fine Arts</t>
+          <t>MFA Painting</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -68957,7 +69025,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>https://www.diegojuarez.com/</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
           <t>Temple/Tyler</t>
@@ -68971,7 +69043,7 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: April 16- April 19); no email/major/portfolio published on source page</t>
+          <t>Personal site found via web search (diegojuarez.com/bio) but no email visible — only Instagram link and a /contact link not checked; no email found</t>
         </is>
       </c>
     </row>
@@ -68984,7 +69056,7 @@
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MFA Fine Arts</t>
+          <t>MFA Painting</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -69006,7 +69078,7 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: April 16- April 19); no email/major/portfolio published on source page</t>
+          <t>No email found via web search — no personal site surfaced</t>
         </is>
       </c>
     </row>
@@ -69019,7 +69091,7 @@
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MFA Fine Arts</t>
+          <t>MFA Graphic Design</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -69041,7 +69113,7 @@
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: April 23 - April 26); no email/major/portfolio published on source page</t>
+          <t>No email found via web search — no personal site surfaced</t>
         </is>
       </c>
     </row>
@@ -69054,7 +69126,7 @@
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MFA Fine Arts</t>
+          <t>MFA Graphic Design</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -69076,7 +69148,7 @@
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: April 23 - April 26); no email/major/portfolio published on source page</t>
+          <t>No email found via web search — no personal site surfaced; works at Running Press Book Publishers</t>
         </is>
       </c>
     </row>
@@ -69089,7 +69161,7 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MFA Fine Arts</t>
+          <t>MFA Design</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -69097,7 +69169,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>https://pegahsaebi.com/</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
           <t>Temple/Tyler</t>
@@ -69111,7 +69187,7 @@
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: April 23 - April 26); no email/major/portfolio published on source page</t>
+          <t>Own site (pegahsaebi.com) found via web search but could not be resolved by this tool's fetcher (DNS failure) — try visiting manually</t>
         </is>
       </c>
     </row>

--- a/Dezi Art Prize Student Data Scraping/master_students.xlsx
+++ b/Dezi Art Prize Student Data Scraping/master_students.xlsx
@@ -13252,7 +13252,11 @@
           <t>Walter Smits</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>smits.walt@gmail.com</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>MFA Studio Art (First-Year MFA)</t>
@@ -13277,7 +13281,7 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Own site returned HTTP 503 (site appears down) on repeated fetch attempts; CMU directory page has no direct email listed — try visiting waltersmits.com manually</t>
+          <t>Email confirmed by user (site was returning HTTP 503 on repeated fetch attempts by this tool)</t>
         </is>
       </c>
     </row>
@@ -13322,7 +13326,11 @@
           <t>Yiying Wang</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>yiyingwang194@gmail.com</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
           <t>MFA Studio Art (First-Year MFA)</t>
@@ -13347,7 +13355,7 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Own site (yiyingwang666.com) could not be resolved by this tool's fetcher (DNS failure) — try visiting manually; CMU directory page has no direct email listed</t>
+          <t>Email confirmed by user (site was unresolvable by this tool's fetcher)</t>
         </is>
       </c>
     </row>
@@ -31460,7 +31468,11 @@
           <t>Lisa Spencer</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>lisaspencergallery@gmail.com</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
           <t>MFA Photography</t>
@@ -31489,7 +31501,7 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Photographer/writer based in Winchester, MA; Visura profile found via web search but returned HTTP 403 on fetch — no email found</t>
+          <t>Email confirmed by user</t>
         </is>
       </c>
     </row>
@@ -31663,7 +31675,11 @@
           <t>Suzi Grossman</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Photo@suzigrossman.com</t>
+        </is>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
           <t>MFA Photography</t>
@@ -31692,7 +31708,7 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>UNVERIFIED possible email: Suzi@suzigrossman.com — surfaced via web search summary of the site's contact page, but the email is JS-obfuscated on the live page and could not be independently confirmed by direct fetch; not written as confirmed</t>
+          <t>Email confirmed by user (different address than the earlier unverified search-summary guess)</t>
         </is>
       </c>
     </row>
@@ -47137,7 +47153,11 @@
           <t>Li-Yuan Chiou</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>lychiou@uw.edu</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>MFA/MDes (UW Art — discipline not specified per student)</t>
@@ -47166,7 +47186,7 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Name only, from Henry Art Gallery thesis exhibition page; no email/portfolio published; source page does not map a specific discipline to each individual student</t>
+          <t>Email confirmed by user (UW address)</t>
         </is>
       </c>
     </row>
@@ -47215,7 +47235,11 @@
           <t>Victoria Mackender</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>victoriaa961@gmail.com</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
           <t>MFA/MDes (UW Art — discipline not specified per student)</t>
@@ -47244,7 +47268,7 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Personal site found via web search (vamack.com) but this tool's fetcher could not resolve the domain (DNS failure) — try visiting manually for contact info; also has Instagram @vamackender</t>
+          <t>Email confirmed by user via vamack.com (manual check, DNS-unreachable by this tool)</t>
         </is>
       </c>
     </row>
@@ -47293,7 +47317,11 @@
           <t>Oscar Pearson</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>o2thescar@hotmail.com</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr">
         <is>
           <t>MFA/MDes (UW Art — discipline not specified per student)</t>
@@ -47322,7 +47350,7 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Personal site found via web search (Wix site, Instagram @oscarpearson_) but no email visible — only a Wix contact form; no email found. NOTE: a different, unrelated Oscar Pearson (California muralist/gallery artist) also shows up in search — not to be confused with this student</t>
+          <t>Email confirmed by user. NOTE: a different, unrelated Oscar Pearson (California muralist/gallery artist) also shows up in search — not to be confused with this student</t>
         </is>
       </c>
     </row>
@@ -47332,7 +47360,11 @@
           <t>Chave Pichardo</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>chavepichardostudios@gmail.com</t>
+        </is>
+      </c>
       <c r="C13" t="inlineStr">
         <is>
           <t>MFA/MDes (UW Art — discipline not specified per student)</t>
@@ -47361,7 +47393,7 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Name only, from Henry Art Gallery thesis exhibition page; no email/portfolio published; source page does not map a specific discipline to each individual student</t>
+          <t>Email confirmed by user</t>
         </is>
       </c>
     </row>
@@ -47371,7 +47403,11 @@
           <t>Andrew Roibal</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>AndrewRoibalArt@gmail.com</t>
+        </is>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
           <t>MFA/MDes (UW Art — discipline not specified per student)</t>
@@ -47384,7 +47420,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://henryart.org/exhibitions/2026-university-of-washington-mfa-mdes-thesis-exhibition</t>
+          <t>https://art.washington.edu/people/andrew-roibal</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -47400,7 +47436,7 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Name only, from Henry Art Gallery thesis exhibition page; no email/portfolio published; source page does not map a specific discipline to each individual student</t>
+          <t>Email confirmed by user (also has UW address aroibal@uw.edu)</t>
         </is>
       </c>
     </row>
@@ -47410,7 +47446,11 @@
           <t>Ryan Walters</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>RyanWaltersFilms@gmail.com</t>
+        </is>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
           <t>MFA/MDes (UW Art — discipline not specified per student)</t>
@@ -47439,7 +47479,7 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Personal site found via web search (ryanwalters.art) but this tool's fetcher could not resolve the .art domain (DNS failure) — try visiting manually for contact info</t>
+          <t>Email confirmed by user via ryanwalters.art (manual check, .art domain unreachable by this tool)</t>
         </is>
       </c>
     </row>
@@ -68114,7 +68154,11 @@
           <t>Natalia Purchiaroni</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>npurchphotography@gmail.com</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>MFA Photography</t>
@@ -68139,7 +68183,7 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>No email found via web search — no personal site surfaced</t>
+          <t>Email confirmed by user</t>
         </is>
       </c>
     </row>
@@ -68149,7 +68193,11 @@
           <t>Macy West</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>macywest99@gmail.com</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>MFA Fine Arts</t>
@@ -68174,7 +68222,7 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>No email found via web search — no personal site surfaced</t>
+          <t>Email confirmed by user</t>
         </is>
       </c>
     </row>
@@ -68256,7 +68304,7 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Own site (fernandanunez.com) found via web search but returned HTTP 503 on fetch — try visiting manually</t>
+          <t>Own site (fernandanunez.com) found via web search but returned HTTP 503 on fetch; not resolved this pass — still needs manual check</t>
         </is>
       </c>
     </row>
@@ -68266,7 +68314,11 @@
           <t>Mika Obayashi</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>mikacobayashi@gmail.com</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
           <t>MFA Fiber/Sculpture</t>
@@ -68295,7 +68347,7 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Personal site found via web search (mikaobayashi.com) but no email visible — only Instagram and a /contact link; no email found</t>
+          <t>Email confirmed by user</t>
         </is>
       </c>
     </row>
@@ -68305,7 +68357,11 @@
           <t>Heather Swenson</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Mail@heatherswenson.com</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr">
         <is>
           <t>MFA Painting</t>
@@ -68316,7 +68372,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://www.heatherswenson.com/</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>Temple/Tyler</t>
@@ -68330,7 +68390,7 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>No email found via web search — no personal site surfaced</t>
+          <t>Email confirmed by user (own site heatherswenson.com)</t>
         </is>
       </c>
     </row>
@@ -68340,7 +68400,11 @@
           <t>Sophia Dell'Arciprete</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>sophiadellarciprete@yahoo.com</t>
+        </is>
+      </c>
       <c r="C13" t="inlineStr">
         <is>
           <t>MFA Photography</t>
@@ -68369,7 +68433,7 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Personal site found via web search (sophiadellarciprete.com) but no email visible in static HTML; no email found</t>
+          <t>Email confirmed by user</t>
         </is>
       </c>
     </row>
@@ -68465,7 +68529,11 @@
           <t>Ari Zuaro</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>azuaro@theclaystudio.org</t>
+        </is>
+      </c>
       <c r="C16" t="inlineStr">
         <is>
           <t>MFA Ceramics</t>
@@ -68494,7 +68562,7 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Personal site found via web search (arizuaro.com) but no email visible — only Instagram link; no email found</t>
+          <t>Email confirmed by user (Clay Studio staff address, where they also work)</t>
         </is>
       </c>
     </row>
@@ -68617,7 +68685,11 @@
           <t>Esther Park</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>eyparkart7@gmail.com</t>
+        </is>
+      </c>
       <c r="C20" t="inlineStr">
         <is>
           <t>MFA Fine Arts</t>
@@ -68642,7 +68714,7 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>No email found via web search — no personal site surfaced</t>
+          <t>Email confirmed by user</t>
         </is>
       </c>
     </row>
@@ -68652,7 +68724,11 @@
           <t>Mollie Hansen</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>mollie.hansen.art@gmail.com</t>
+        </is>
+      </c>
       <c r="C21" t="inlineStr">
         <is>
           <t>MFA Fine Arts</t>
@@ -68677,7 +68753,7 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>No email found via web search — no personal site surfaced</t>
+          <t>Email confirmed by user</t>
         </is>
       </c>
     </row>
@@ -68687,7 +68763,11 @@
           <t>Maedeh Mehdipour</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>mehdipour.maede@gmail.com</t>
+        </is>
+      </c>
       <c r="C22" t="inlineStr">
         <is>
           <t>MFA Fiber and Material Studies</t>
@@ -68716,7 +68796,7 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Personal site found via web search (maedehmehdipour.com) but returned HTTP 403 on fetch — could not retrieve email; try visiting manually</t>
+          <t>Email confirmed by user (site was returning HTTP 403 on fetch by this tool)</t>
         </is>
       </c>
     </row>
@@ -68761,7 +68841,11 @@
           <t>Madeline Rodriguez</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>rodriguez.maddie@gmail.com</t>
+        </is>
+      </c>
       <c r="C24" t="inlineStr">
         <is>
           <t>MFA Fine Arts</t>
@@ -68786,7 +68870,7 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>No email found via web search — no personal site surfaced</t>
+          <t>Email confirmed by user</t>
         </is>
       </c>
     </row>
@@ -68831,7 +68915,11 @@
           <t>Ivy Jewell</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ijewell@theclaystudio.org</t>
+        </is>
+      </c>
       <c r="C26" t="inlineStr">
         <is>
           <t>MFA Fine Arts</t>
@@ -68856,7 +68944,7 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>No email found via web search — no personal site surfaced</t>
+          <t>Email confirmed by user (Clay Studio staff address)</t>
         </is>
       </c>
     </row>
@@ -68866,7 +68954,11 @@
           <t>Angelique Scott</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ArtByAngeliqueScott@gmail.com</t>
+        </is>
+      </c>
       <c r="C27" t="inlineStr">
         <is>
           <t>MFA Fine Arts</t>
@@ -68891,7 +68983,7 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>No email found via web search — no personal site surfaced</t>
+          <t>Email confirmed by user</t>
         </is>
       </c>
     </row>
@@ -68901,7 +68993,11 @@
           <t>Ben Solo</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>benweidlich.bs@gmail.com</t>
+        </is>
+      </c>
       <c r="C28" t="inlineStr">
         <is>
           <t>MFA Fine Arts</t>
@@ -68930,7 +69026,7 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Own site (bensoloart.com) found via web search but could not be resolved by this tool's fetcher (DNS failure) — try visiting manually</t>
+          <t>Email confirmed by user (real name appears to be Ben Weidlich; site was unresolvable by this tool's fetcher)</t>
         </is>
       </c>
     </row>
@@ -68940,7 +69036,11 @@
           <t>Logan Crompton</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>lcrompton@kcai.edu</t>
+        </is>
+      </c>
       <c r="C29" t="inlineStr">
         <is>
           <t>MFA Fine Arts</t>
@@ -68969,7 +69069,7 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Link-in-bio page (scoby.page) found via web search — not fetched for email this pass</t>
+          <t>Email confirmed by user (Kansas City Art Institute address)</t>
         </is>
       </c>
     </row>
@@ -68979,7 +69079,11 @@
           <t>Boi Boy</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>boiboy.art@gmail.com</t>
+        </is>
+      </c>
       <c r="C30" t="inlineStr">
         <is>
           <t>MFA Fine Arts</t>
@@ -69004,7 +69108,7 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>No email found via web search — no personal site surfaced (full name may be 'Boi Boy Cottrell' per one source)</t>
+          <t>Email confirmed by user (full name may be 'Boi Boy Cottrell' per one source)</t>
         </is>
       </c>
     </row>
@@ -69014,7 +69118,11 @@
           <t>Diego Juarez</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>juarezcdiego@gmail.com</t>
+        </is>
+      </c>
       <c r="C31" t="inlineStr">
         <is>
           <t>MFA Painting</t>
@@ -69043,7 +69151,7 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Personal site found via web search (diegojuarez.com/bio) but no email visible — only Instagram link and a /contact link not checked; no email found</t>
+          <t>Email confirmed by user</t>
         </is>
       </c>
     </row>
@@ -69053,7 +69161,11 @@
           <t>Gianna Santucci</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>gsantucci630@gmail.com</t>
+        </is>
+      </c>
       <c r="C32" t="inlineStr">
         <is>
           <t>MFA Painting</t>
@@ -69078,7 +69190,7 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>No email found via web search — no personal site surfaced</t>
+          <t>Email confirmed by user</t>
         </is>
       </c>
     </row>
@@ -69158,7 +69270,11 @@
           <t>Pegah Saebi</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>pegah.saebi96@gmail.com</t>
+        </is>
+      </c>
       <c r="C35" t="inlineStr">
         <is>
           <t>MFA Design</t>
@@ -69187,7 +69303,7 @@
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Own site (pegahsaebi.com) found via web search but could not be resolved by this tool's fetcher (DNS failure) — try visiting manually</t>
+          <t>Email confirmed by user (site was unresolvable by this tool's fetcher)</t>
         </is>
       </c>
     </row>

--- a/Dezi Art Prize Student Data Scraping/master_students.xlsx
+++ b/Dezi Art Prize Student Data Scraping/master_students.xlsx
@@ -32,6 +32,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Iowa" sheetId="23" state="visible" r:id="rId23"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UW Art" sheetId="24" state="visible" r:id="rId24"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BGSU" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CalArts Animation" sheetId="26" state="visible" r:id="rId26"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'RIT'!$A$5:$I$326</definedName>
@@ -59,6 +60,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'Iowa'!$A$5:$I$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'UW Art'!$A$5:$I$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'BGSU'!$A$5:$I$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'CalArts Animation'!$A$5:$I$256</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -45782,7 +45784,7 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BFA/BA Fine Art (C33 Gallery)</t>
+          <t>BFA Fine Art (C33 Gallery)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -45792,7 +45794,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+          <t>https://www.creatingbyjenna.art/</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -45808,7 +45810,7 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Name only, from 'C33 Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published</t>
+          <t>Personal site found via web search (creatingbyjenna.art) but no email visible — only Instagram/TikTok/YouTube and an unfetched /contact page; no email found</t>
         </is>
       </c>
     </row>
@@ -45899,7 +45901,7 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BFA/BA Fine Art (C33 Gallery)</t>
+          <t>BFA Fine Art (C33 Gallery)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -45909,7 +45911,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+          <t>https://shop.colum.edu/lobotomy-by-ana-lara.html</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -45925,7 +45927,7 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Name only, from 'C33 Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published</t>
+          <t>Confirmed as a Columbia Fine Arts student via ShopColumbia listing ('Lobotomy' by Ana Lara) but no email found — ShopColumbia has no direct artist contact page</t>
         </is>
       </c>
     </row>
@@ -46055,7 +46057,7 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BFA/BA Fine Art (C33 Gallery)</t>
+          <t>BFA Fine Art (C33 Gallery)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -46081,7 +46083,7 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Name only, from 'C33 Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published</t>
+          <t>No email found — multiple different people share this name online (a Chicago mixed-media artist, a UIC student, a musician endorser); none confirmed as the same Columbia College Chicago student, so not treated as a match</t>
         </is>
       </c>
     </row>
@@ -47849,6 +47851,9897 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I256"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Source: CalArts Film/Video Animation Student Portfolios, 2026 — Character Animation (BFA 1-4, Affiliates, Recent Alumni) and Experimental Animation (BFA 1-4, MFA 1-3, Recent Alumni), 14 pages total. Each student entry includes name, class year, specialization, and Resume/Email/Portfolio/social links in plain static HTML (no JS rendering needed). Distinct from the separate 'CalArts' source (High Pass BFA exhibition, names only, no email).</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>URL: https://calarts.edu/filmvideo/animation-student-portfolios/2026/character-animation and .../experimental-animation (14 sub-pages: bfa-1 through bfa-4, affiliates, recent-alumni, mfa-1 through mfa-3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Accessed: 2026-08-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>graduation_year</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>portfolio_url</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>college</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>contacted</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Lauren Addington</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>laurenaddington@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 1) — Character Design / Storyboarding</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://laurenaddingtonportfolio.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1NgBzbPeVvnsPFSuDAB1kuZY9fMrLUMp0cAUSo5P46f4/edit?usp=drivesdk; Instagram: https://www.instagram.com/bungeeart/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Agnès-Hana Boudrant</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>agneshanaboudrant@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 1) — 2D Animation / Storyboarding / Character Design</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://agnesboudrant.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1mmkk7cht-QLjmVzD6SuXL5qN0fn8qBgEcnD_Vv5K510/edit?usp=sharing; Instagram: https://www.instagram.com/ahnyeshana/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Candace Choi</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>candacechoi@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 1) — Character Design / Storyboarding</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://candacechoi.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1QjIcenbK5NRzu91n1tDRET--PTgA6HP6q3frfcKSEWs/edit?usp=sharing; Instagram: https://www.instagram.com/dacenart/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Haerim Choi</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>haerimchoi@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 1) — 2D Animation / Visual Development, Background Design / Stop-Motion, Puppetry</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://haerimchoi.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1BOSbInOcC8PXSySqDiUEGcx7V_x8fDtNj7gELtA-mLw/edit?usp=sharing; Instagram: https://www.instagram.com/haerimuchoi/; Youtube: https://youtube.com/channel/UCzcoRuULzaX27EJx2brknpg?si=n-3FEQD-X_DB0ERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Jisoo Chong</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>jisoochong@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 1) — Character Design / 2D Animation</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>http://jisoochong.weebly.com</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1BrDAscDPhJco0xM9CQELukf7KN2rfTIVyJAWViD5_84/edit?usp=sharing; Instagram: https://www.instagram.com/soda.seas</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Jenna Cui</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>jennacui@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 1) — Storyboarding / 2D Animation</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://jennacui.wixsite.com/portfolio</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/10wKEc88bmVD7cIMwhnCrVR5fE3AquNhHLkUKpRZ5jpY/edit?usp=sharing; Instagram: https://www.instagram.com/evincives</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Sally Cui</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>sallycui@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 1) — Storyboarding / Character Design</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://sallycui.weebly.com</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1h-7v7SkP0cMvqzCKy9j-INRveMUVMA4auUAGIxe08e0/edit?usp=sharing; Instagram: https://www.instagram.com/avo_credo</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Van Del Prete</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>edelprete@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 1) — Character Design / Storyboarding / Writing for Animation</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://vandelprete.weebly.com</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1Cx93XJoX548LKTdM0_-eySP6mI4wAdNFPdEapSOixac/edit?usp=sharing; Instagram: https://www.instagram.com/jig_jag_/; Youtube: https://www.youtube.com/@Jig_Jag_/videos</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Stephanie Feng</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>stephaniefeng@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 1) — Character Design / Illustration, Comics</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://stephaniefeng.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1L02CVxkESylPJCvI1NqhNkTpIpIDsKblMoJDaVECbr0/edit?usp=sharing; Instagram: https://www.instagram.com/glaxierr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Molly Fyfe</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>mfyfe@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 1) — Character Design / Visual Development, Background Design</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://www.mollyfyfe.com/</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/13GCjOvxTV6c4_tQOXlGXi_4W3FZT2NgBlQeTV1eVkcA/edit?usp=sharing; Instagram: https://www.instagram.com/frostingfluff/; Youtube: https://www.youtube.com/@frostingfluff/videos</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Anita Guo</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>anitaguo@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 1) — Character Design / Visual Development, Background Design / 2D Animation</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://10geckoatoms.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/10HI4mB5mR1go3LrSVwzkRX2hT0gOlkBiIV9AHwSI9tU/edit?usp=drivesdk; Instagram: https://www.instagram.com/10geckoatoms; Youtube: https://www.youtube.com/@gawrgurant5721</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Quillen Ham</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>quillenham@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 1) — 2D Animation / Writing for Animation / Independent Filmmaking</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://quillenhamarts.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1Xez0vrAKxo0j0kyZkU2QlPTAtkbr0o0-jKqzLJO4MVQ/edit?usp=sharing; Instagram: https://www.instagram.com/forgetmesoup/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Elsa Heinrich</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>eheinrich@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 1) — Storyboarding / Character Design</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://elsaheinrich.weebly.com</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/180TYXcJCXmD0q1ipOfnjHJDgr_yzde5HG7DNgajwYdo/edit?tab=t.0; Instagram: https://www.instagram.com/elsarhart/; Youtube: https://www.youtube.com/@elsarhart</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Stone Huang</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>alicehuang@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 1) — Storyboarding / Illustration, Comics</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://stonehuang.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1vTdcV9ZJTcPpVLDmB2NLZScLT9GvD8kJAZe9fHhHtK4/edit?usp=sharing; Instagram: https://www.instagram.com/dusi_tong/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Allisa Johnson</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>allisajohnson@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 1) — Illustration, Comics / CG Modeling, Rigging, Texturing / 2D Animation</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>https://allisaj.weebly.com</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1i6OGxNs08o7QhzGGCK-fpWSyOxxCARoykklVOlFGONM/edit?tab=t.0; Instagram: https://www.instagram.com/bugdog_arts</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Mac Kayser</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>mackayser@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 1) — Storyboarding / Visual Development, Background Design</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://www.mackayserart.com/</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1Gpf0Wor-8CK6cm7KodStBGi-Y8t09bywyzNLwaKx5Q8/edit?usp=sharing; Instagram: https://www.instagram.com/spacemicrowave/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Taran Krishna</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>tkrishna@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 1) — Visual Development, Background Design / Character Design / Experimental Techniques</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/drive/folders/11wfOdVvd6jw_DbNQHjZXhIq-KqGsp2MB?usp=drive_link</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/16dxnM9PArrt88w9m9-5P1Y2LsQQn5Fqe1nB4bibXyiw/edit?usp=sharing; Instagram: https://www.instagram.com/snowcupie/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Amane Lee</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>amanelee@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 1) — Visual Development, Background Design / Character Design / Storyboarding</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://amaneshingakilee.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1Px33m3DX6HljdRm8_cAoR-_vuXZ1zNSF0rV_2cJ_8FA/edit?usp=drive_link; Instagram: https://www.instagram.com/amaneshingaki/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Nayoun Lee</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>nayounlee@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 1) — Character Design / 2D Animation</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://bayousleg.wixsite.com/nayounlee</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1VusT7SNq-KQdRiJVc0Uns9dKPxAklv-q-wS5MsSm-6Y/edit?tab=t.0; Instagram: https://www.instagram.com/bayous.leg</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Cyrus Leung</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>cyrusleung@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 1) — Character Design / Visual Development, Background Design / Storyboarding</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/drive/folders/1CDRMU5B4oIZtju6fMX3g9fY0a_xBCJuB?usp=sharing</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1h2iT6FcysiXklSEgYuDsXz0PAplwN2quSiTLPp4Epe0/edit?usp=sharing; Instagram: https://www.instagram.com/saticoh890/; Youtube: https://www.youtube.com/@nuparu7991/videos</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Kelly Li</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>kellyli@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 1) — 2D Animation / Character Design / CG Animation</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://imkellyli.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1U7J8jtMnZSHFgev1j-BRiMmP1s_KB_h-IOv0t3EGyLI/edit?usp=sharing; Instagram: https://www.instagram.com/susu4.o_o/; Youtube: https://www.youtube.com/@susu0175</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Ting-Ting Lian</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>tingtinglian@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 1) — 2D Animation / Storyboarding / Illustration, Comics</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://tingtingylianportfolio.weebly.com</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1r7pbIkezSblXvORff1YaVuFa74BZmM7N3AJtRUMGTcE/edit?usp=sharing; Instagram: https://www.instagram.com/t_egg0/; Youtube: https://www.youtube.com/@crispytomato543</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Angela Lin</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>angelalin@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 1) — Visual Development, Background Design / Character Design / Storyboarding</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>https://angelalinjy.wixsite.com/angelalin</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1p4ltTPfd054AcPKoWHK9UQ_THJ1vPiqM/edit?usp=drivesdk&amp;ouid=111116364503596289246&amp;rtpof=true&amp;sd=true; Instagram: https://www.instagram.com/plotlesspasta</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Nana Liu</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>naomiliu@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 1) — Experimental Techniques / 2D Animation / Independent Filmmaking</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>https://nanaliu0729.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1Wx-Ol57xaPjEuNLycgAN4xDXK0PJYqeZboyKBK5qphY/edit?usp=sharing; Instagram: https://www.instagram.com/essunanana; Youtube: https://www.youtube.com/@essunanana</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Tina Liu</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>tinaliu@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 1) — Storyboarding / Character Design / Visual Development, Background Design</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>https://tinaliustory.weebly.com</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1tXDbeWGM0yzH6dRMujkodK0a4CjpaVC0Sf8_64H8yDs/edit?usp=sharing; Instagram: https://www.instagram.com/anit.una</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Mandi Lu</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>mandilu@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 1) — Visual Development, Background Design / Illustration, Comics / Character Design</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>https://www.mandi-lu.com</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1OVIGn84tJLlSj25M7KxtfcCeD0ztM1g3iLePUtDJ188/edit?usp=sharing; Instagram: https://www.instagram.com/mimizu330</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Pearl Lu</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>jinhengcao@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 1) — Character Design / Storyboarding / Illustration, Comics</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/drive/folders/13RLYOQ_a7h1-SphVn4idJPKP5u3zo67f</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1-KcinpasqglAL5CI7n2j6QnoDD-4zvRyvPov4Zfe1uE/edit?usp=drivesdk; Instagram: https://www.instagram.com/pelolu_</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Crystal Mao</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>crystalmao@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 1) — 2D Animation / Character Design</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://crystalmao.weebly.com</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1atrb88bYmzCaTEEh5OWy4MqOUK3gE7z1L-AymNSgJ5E/edit?usp=sharing; Instagram: https://www.instagram.com/craastle</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Molly Mock</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>mollymock@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 1) — Writing for Animation / Storyboarding / Independent Filmmaking</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://mollymock.art</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1dKnfmPfI5WyJNR4vcVOeeNdya6K9E9i4Nw9oB1aRS2s/edit?usp=sharing; Instagram: https://www.instagram.com/mollymock/; Youtube: https://www.youtube.com/@molly_mock</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Isabella Montesi</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>imontesi@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 1) — Storyboarding / Independent Filmmaking / Character Design</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>https://isabellamontesi.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/12RQQXrPMvREoDMlK4lBPB7fHiHe0oLLDVUzEY4ck_HM/edit?usp=drivesdk; Instagram: https://www.instagram.com/miynomo; Youtube: https://www.youtube.com/@miynomo</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Liam Nagel</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>liamnagel@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 1) — Illustration, Comics / 2D Animation / Character Design</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>https://voidblade2.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/18jlcvJAwI24IWAXlMYwH0GAm8son88BM5zQSEeqz3r4/edit?usp=sharing; Instagram: https://www.instagram.com/sucky_drawings_9/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Ren Olson</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>renolson@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 1) — Storyboarding / Writing for Animation</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://renolson.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1ViL5HsLmSLATS-cBPZudTjIZw1YqdjXMUu3qixZBvzQ/edit?usp=sharing; Instagram: https://www.instagram.com/rentoonz</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Sofia Palacios</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>sofiapalacios@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 1) — Character Design / Visual Development, Background Design</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://sofiapalacios.cargo.site/</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1-MOET_sI5-MFBORItzUeBGtqnkyXIwgMx5I9n7-wA6E/edit?usp=drivesdk; Instagram: https://www.instagram.com/fiacios/; LinkedIn: https://www.linkedin.com/in/sofia-palacios-220bb8248</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Tori Pham</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>victoriapham@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 1) — Storyboarding / Character Design / Illustration, Comics</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>http://artorian.wixsite.com/portfolio</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1lA_lzfNoy2N48w2diLGduCxAy7x3oQKQRVnMCg7kEp4/edit?usp=sharing; Instagram: https://www.instagram.com/artorian/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Julia Pohontu</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>juliapohontu@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 1) — Character Design / Visual Development, Background Design / 2D Animation</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>https://juliapohontu.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1_wI53VR7TD_04FfSYEjraGpD2-k-TI-do9W-_rsYOZk/edit?usp=sharing; Instagram: https://www.instagram.com/juliaugh/</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Kohana Porter</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>kporter@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 1) — Storyboarding / Writing for Animation / Character Design</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>https://kohanaporter.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1nmS0dnRdWKXLTuXupuLAfOZ99g0ykkkRjsUmDqXr8ts/edit?usp=sharing; Instagram: https://www.instagram.com/fishstigures/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Jadyn Richardson</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>jadynrichardson@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 1) — Character Design / 2D Animation / Storyboarding</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>https://denjasketches.myportfolio.com/</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1_8xFMTot33Azsd1aPYVmpNdHD9204ZYl/edit?usp=sharing&amp;ouid=107968453453012187377&amp;rtpof=true&amp;sd=true; Instagram: https://www.instagram.com/denjasketches/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Reign Sanchez</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>rsanchez@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 1) — Visual Development, Background Design / Character Design / Illustration, Comics</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://reignsanchezarts.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1z8aYA2pGTU8Kuzzp6rBAQDsLcRaDC-sB8GJ0a3dCX3g/edit?usp=sharing; Instagram: https://www.instagram.com/reghosty_</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Chloe Szep</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>cszep@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 1) — Visual Development, Background Design / Storyboarding / Content Creation for Social Media</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>https://www.chloeszep.com/</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1mkC47p28G-iXSb6R-PRNMNRsCC0PWOSvCgVVxm1XugA/edit?tab=t.0; Instagram: https://www.instagram.com/moonialin</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Jianan (Jackson) Wang</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>jacksonwang@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 1) — Visual Development, Background Design / 2D Animation</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>https://jwang15.myportfolio.com/</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Resume: https://drive.google.com/drive/folders/1L4TuSM6qko4Symr4Y-9YH2YVyRFdvGa7?usp=sharing; Instagram: https://www.instagram.com/jwang152019/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Amira Warren</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>amirawarren@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 1) — Character Design</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://amirawarren.weebly.com</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1BfwzBIQIV0YiosVrGy82ywRrJ35gaYZ4UAoj1d_PUSw/edit?usp=sharing; Instagram: https://www.instagram.com/starsaw__/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Jack Wu</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>jackwu@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 1) — Visual Development, Background Design / Storyboarding</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://jackwuart.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1VjovOCChmc9yz2FKOjrmkAZlbrPQnPSQtQiwIeaM5aE/edit?usp=sharing; Instagram: https://www.instagram.com/jwooshu/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Mylo Yoon</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>myloyoon@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 1) — Storyboarding / Visual Development, Background Design</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>https://jiwoo2464.wixsite.com/myloyoon</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1q-owvmii5KE_hf6YNtCFNuIQO-QVBOxrbCeRpuwz_ZY/edit?usp=sharing; Instagram: https://www.instagram.com/mystmyong</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Angel Zhang</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>angelzhang@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 1) — 2D Animation / Color Design / Game Design</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://angzhang.weebly.com</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1P7ESEna1vPE0E-PCPN3MMl_cXWCWg2OLuoMzLYDfkLo/edit?usp=sharing; Instagram: https://www.instagram.com/c4roussl</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Emily Chang</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>shuchichang@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 2) — Visual Development, Background Design / Character Design / Prop Design</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://emilychangportfolio.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1AgHD1jT0OTIq_isTUvq05t60ozbHW9ewlqwBAsryHKk/edit?usp=drivesdk; Instagram: https://www.instagram.com/zhiiart0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Shannon Chen</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>shannonxchen@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 2) — Character Design / Storyboarding</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://shannonchen.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1kZjj048QyoZNqxZ4c2qc3cYml1KzGf8v/edit?usp=drivesdk&amp;ouid=111905990644100628947&amp;rtpof=true&amp;sd=true; Instagram: https://www.instagram.com/fii.sh</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Melody Chiang</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>melodychiang@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 2) — Storyboarding / Visual Development, Background Design</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://melodychiangm3l.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1j3j88VKP9D7gdcsCk5qoUqiq4XfL_BHCB_WP_LMDH5Q/edit?usp=drivesdk; Instagram: https://www.instagram.com/m3lody.j</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gyumin Choi</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gyuminchoi@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 2) — Visual Development, Background Design / 2D Animation / CG Animation</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://gyuminchoi.myportfolio.com/</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/14E1rsYD0AHPm0MqRbk8M9EgRb-NpmyPPHevjDopwflI/edit?usp=drive_link; Instagram: https://www.instagram.com/min.choi_i/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Audrey Chow</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>audreychow@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 2) — Illustration, Comics / Visual Development, Background Design / Storyboarding</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://audrey-art.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/11EzTHaAJpm6zf1PgvcAk3ZSeji4PtR4tLVbFPJ5jiaQ/edit?usp=drivesdk; Instagram: https://www.instagram.com/yu_yuao; Youtube: https://www.youtube.com/@yu_yuao/videos</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Apoorva Dasari</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>apoorvadasari@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 2) — Visual Development, Background Design / Character Design / Illustration, Comics</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://apoorvadasari.com/</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/17Js2GmJAKek87zNPw5e1lRsUS-F_GL2taGmf3bjV69Q/edit?usp=drivesdk; Instagram: https://www.instagram.com/grackle_queen; LinkedIn: http://www.linkedin.com/in/apoorva-dasari-0960a1252</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Niq Ducote</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>nducote@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 2) — Character Design / Prop Design / Visual Development, Background Design</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://niqducote.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/10p6wsTQGVDUJUfL1DMVLoiz-MpuUr_Dt_ju-KCDV1Mk/edit?usp=drivesdk; Instagram: https://www.instagram.com/niqducoteart/; Youtube: https://www.youtube.com/@NiqDucoteArt/videos</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Yuwei Feng</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>yuweifeng@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 2) — 2D Animation / Character Design / Illustration, Comics</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/drive/folders/1oELjP-6cmI2YYlJ6t8dwadgjq3wru95a?usp=sharing</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1oEQuKzHClU4hT8buNt-fg0eilPJz2_GZCbwupWQXOT4/edit?usp=sharing; Instagram: https://www.instagram.com/q1ng_y1</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Genevieve Funes</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>genevievefunes@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 2) — 2D Animation / Character Design / Visual Development, Background Design</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://genfunes.myportfolio.com/</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1jQUpTSTW_fRF3vLFJLhOeDGUB8q1Bep7kIpI1621SSs/edit?usp=sharing; Instagram: https://www.instagram.com/manysketchbooks; Youtube: https://www.youtube.com/@manysketchbooks</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Kaylie Haggenmiller</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>kayliehaggenmiller@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 2) — Character Design / Visual Development, Background Design</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://kayliehaggenmiller.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1lZp8eshVsLQKS98wrHFH_kYvv8odVU79Az4mGi-p0QA/edit?usp=drivesdk; Instagram: https://www.instagram.com/kayliesartaccount; Youtube: https://www.youtube.com/@kayliesartaccount/videos</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Celine Hung</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>celinehung@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 2) — 2D Animation / Illustration, Comics</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://celinehung.myportfolio.com/</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1k0xbKZBU658cGD6BoSnQzlomKMSOmaFdMn9Rm4T6DHE/edit?usp=sharing; Instagram: https://www.instagram.com/wrappedonigiri/; Youtube: https://www.youtube.com/@wrappedonigiri/</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Dylan Johnson</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>dylanjohnson@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 2) — 2D Animation / Character Design / Visual Development, Background Design</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://dylanjohnson.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/14Ty0rUkYhYdle8C9HfMRXuYptehtAR04iiWnE4Pj_vY/edit?usp=drivesdk; Instagram: https://www.instagram.com/ottos.toast; Youtube: https://www.youtube.com/@ottostoast/videos</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Elise Jung</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>elisejung@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 2) — Illustration, Comics / Character Design</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://elisejung.myportfolio.com</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1JdnWemVqV319Nf4qGC68asJC27q0IWELiAPioBsqha4/edit?usp=sharing; Instagram: https://www.instagram.com/geeometreedash</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Hana Khan</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>hkhan@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 2) — Visual Development, Background Design / Storyboarding / Illustration, Comics</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>http://hanaisacartoon.squarespace.com/</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Resume: https://drive.google.com/file/d/19dDrcaEgZ5ueCRYlHtvau3mL6V5OSFAd/view?usp=sharing; Instagram: https://www.instagram.com/hanaisacartoon; Youtube: https://www.youtube.com/@hanaisacartoon</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Pincheng Kuo</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Pinchengkuo@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 2) — 2D Animation / Visual Development, Background Design</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://pinchengkuoebe3.myportfolio.com/</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/10a_rdckCLretUVk5CO6fGvleSJGawzqY24PJAOxMs8I/edit?usp=drivesdk; Instagram: https://www.instagram.com/kuopin.30; Youtube: https://www.youtube.com/@%E9%83%AD%E5%93%81%E5%91%88-g9z/videos</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Junyoung Kwon</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>junyoungkwon@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 2) — 2D Animation / Character Design</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://www.junyoungkwon.com</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1UEiMSlp7PflNCN3iLnWebCvwfu9Jxcb61OoydhqLqoM/edit?usp=sharing; Instagram: https://www.instagram.com/mirutail</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Chaewon Lee</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>chaewonlee1@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 2) — Storyboarding / Character Design / 2D Animation</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://chaechaechae.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/16ObFy_cYqLwvQbtzbaPzkH9jgd-ZWE0EgD65PESTt0s/edit?usp=sharing; Instagram: https://www.instagram.com/cwlee.e_e/; Youtube: https://www.youtube.com/@bagofcornchips00/videos</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Grace Seojin Lee</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>graceseojinlee@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 2) — Visual Development, Background Design / Character Design</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://graceseojinlee.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/10poWI4jVhVsu2nCpJjHsIYEzYu1r6guYOI0bnAovUrA/edit?usp=drivesdk; Instagram: https://www.instagram.com/podojam1008; Youtube: https://www.youtube.com/@grapejam1008</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Coco Liu</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>cocoliu@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 2) — Illustration, Comics / 2D Animation</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://coocliuportfolio.blogspot.com/p/blog-page.html</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/10aT33dkSMx4iTHl4AxtD9rvFaa_TuFacZLkas7QydrU/edit?usp=drivesdk; Instagram: https://www.instagram.com/iik022</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Jean Montesinos Mederos</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>jeanmontesinos@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 2) — 2D Animation / Illustration, Comics / Visual Development, Background Design</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://jeanmontesinos.weebly.com</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1jaf3WI1Kti7mfWgZkL6ijyQ3K9ArNn4JdofrnSBp9UY/edit?usp=sharing; Instagram: https://www.instagram.com/jemvein; Youtube: https://www.youtube.com/@jemvein/featured</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Hanaka Oyama</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>hoyama@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 2) — Visual Development, Background Design / Character Design / Illustration, Comics</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>https://hanakaoyama.myportfolio.com/</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/10caMPB7cvVe2LxJzIGpDoE4W0j9PdAXYlaZKDjTG0Bk/edit?usp=sharing; Instagram: https://www.instagram.com/hanakaoyama/; Youtube: https://www.youtube.com/@hanakaoyama</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Dante Peri</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>danteperi@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 2) — Storyboarding / Character Design / Illustration, Comics</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://danteperi.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/12Zl09cNFYvNtEix7FsGKGPJTdchJeaP5/edit?usp=sharing&amp;ouid=103822679285410146031&amp;rtpof=true&amp;sd=true; Instagram: https://www.instagram.com/dante.elephante; Youtube: https://www.youtube.com/@dante.elephante</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Mohe Pinkston</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>mpinkston@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 2) — Independent Filmmaking / Storyboarding / Writing for Animation</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>https://www.papergoldmohe.com/</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/108rBa8W2diME9zDPKw5Yd5GAIEbrh4dg/edit?usp=sharing&amp;ouid=103754954519847882062&amp;rtpof=true&amp;sd=true; Instagram: https://www.instagram.com/papergold_mohe/; Youtube: https://www.youtube.com/@PapergoldMohe</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Maria Prussing</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>mariaprussing@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 2) — 2D Animation / Storyboarding</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>https://raidoki.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1OFpYctgK5cSWfo_BiiF40FIxVQSrSA6IIUjlOsXCRf0/edit; Instagram: https://www.instagram.com/raidoki; Youtube: https://www.youtube.com/@Raidoki/videos</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Madeline Shaw</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>madelineshaw@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 2) — Illustration, Comics / 2D Animation / Visual Development, Background Design</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>https://madelineshaw.myportfolio.com/</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/13rcSKezr_at-RLSjUoEnSnCtuPt1cNVLsklT3QvFBS8/edit?usp=sharing; Instagram: https://www.instagram.com/madelineshaw.jpeg/</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Jordyn Shen</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>jordynshen@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 2) — Character Design / Illustration, Comics / Visual Development, Background Design</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>https://www.tofucatstudios.com/</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1j2lKwMrBaVUDYkjVhVdou-E3mNH0459k/edit; Instagram: https://www.instagram.com/tofu2tofu/; Youtube: https://www.youtube.com/@tofu2tofuTV</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Olivia Sica</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>osica@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 2) — Visual Development, Background Design / Character Design / Prop Design</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>https://olivias1212.wixsite.com/mysite</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1RJLTsaNjfJH4wmlVKY2Kw-jYclJGIBs7a474MXSHkJg/edit?usp=sharing; Instagram: https://www.instagram.com/oliviaduzart</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Qintong Sun</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>qintongsun@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 2) — Color Design / Character Design / Experimental Techniques</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>https://alixsunportfolio.blogspot.com/</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1DVGTsVAScfm643rO3hfK_w1B-gBx5-lbJ3S1KsvcNEE/edit?usp=sharing; Instagram: https://www.instagram.com/aaalix_art</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Van Tang</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>vantang@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 2) — 2D Animation / Teaching, Education / Illustration, Comics</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>http://van-tang-portfolio.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1z9R6uuhAMDr2PlS4bctUzpmEgC2I5n_-1DL5l4yRZEY/edit?usp=sharing; Instagram: https://www.instagram.com/sinamonbunnn/; Youtube: https://www.youtube.com/@sinamonbunnn</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Q Wang</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>shannonwang@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 2) — Character Design / 2D Animation / Illustration, Comics</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://quirinah.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/13CynwZVM5PD-KljSOqy7aqxXnZvMq0gS/edit?usp=drivesdk&amp;ouid=104636684945550898660&amp;rtpof=true&amp;sd=true; Instagram: https://www.instagram.com/quirinahdraws</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Sebastian Zakhem</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>sebastianzakhem@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 2) — Character Design / Storyboarding / Visual Development, Background Design</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://sebastianzakhem.com/</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1Hw486lQwm10lBMYtnUf_UtHLBMB3nPVW7wpr9BIGuDo/edit; Instagram: https://www.instagram.com/korunaandlime</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Rita Zheng</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>ritazheng@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 2) — Visual Development, Background Design / 2D Animation / Storyboarding</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://ritazhengportfolio.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1UzDW929WDetiLj0eSgOEGVu5eyfoiSTYUjk2gq-o0nA/edit?usp=drivesdk; Instagram: https://www.instagram.com/ceuert_9art</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Yoyo Zhu</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>yoyozhu@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 2) — 2D Animation / Illustration, Comics</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://yoyozhu.weebly.com</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1eGHavlIXSauvSfFWhOtkY0CqQaxTDyHU2GfASqShulI/edit?usp=sharing; Instagram: https://www.instagram.com/mynhgo/</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Justine Alameda</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>justinealameda@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 3) — Visual Development, Background Design / Illustration, Comics</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://justineantoinette.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1CyGVjoss06rR4LQMxXQi5dLBTN2JQ_bYV9xBbNW1iTA/edit?usp=sharing; Instagram: https://www.instagram.com/buddaur; Youtube: https://www.youtube.com/@wuddabudda</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Sarah Allen</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>sarahallen@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 3) — Storyboarding / Visual Development, Background Design / Writing for Animation</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://sarahallen-art.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1NmgCdIyAaI6RqrPYEROOm6rZAXTfUstJ6JrDWtcS5FM/edit?tab=t.0; Instagram: https://www.instagram.com/catamiza/</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Ava Azarmi</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>aazarmi@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 3) — Storyboarding / Independent Filmmaking</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://www.avaazarmi.com/</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1PAhSZ2UFWL53N-2-DIJd5J6ftsBoVrjBENO6A1MT6BQ/edit?usp=sharing; Instagram: https://www.instagram.com/yummyavacado/; Youtube: https://www.youtube.com/@yummyavacado/videos</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Paige Baggen</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>paigebaggen@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 3) — Visual Development, Background Design / Illustration, Comics</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>https://paigabeetle.weebly.com</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/13v-owOVjVgPGgAkuL7gI6U73VQA0abn8x98LOZPT0pY/edit?usp=sharing; Instagram: https://www.instagram.com/paigabeetle/</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Himari Chatani</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>hchatani@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 3) — Visual Development, Background Design / Illustration, Comics / Color Design</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>https://himarichatani.myportfolio.com/</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1z3Lry34z4P3x2s1aW49W4CsCsD3BmMrrTA9_sn6WwQY/edit?usp=sharing; Instagram: https://www.instagram.com/himarichatani/; Youtube: https://www.youtube.com/@himarichatani/videos</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Fel Chen</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>felchen@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 3) — 2D Animation / Character Design / Visual Development, Background Design</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://felchen.square.site/</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Resume: https://drive.google.com/file/d/1BYGRtaFvjfdh_skEcxwB7Ckiu8UkG6dc/view?usp=drivesdk; Instagram: https://www.instagram.com/halfassedtea</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Melody Cheng</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>melodycheng@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 3) — Visual Development, Background Design / Character Design / Illustration, Comics</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://melody-cheng.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/12ctW4PSTCqzVBEtBeCR661IT-JWUpwOiTblcNq4Ryg0/edit?usp=sharing; Instagram: https://www.instagram.com/diac.ha/; Youtube: http://www.youtube.com/@melodycheng7451</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Giovanni Edwards</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>giovanniedwards@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 3) — 2D Animation</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://giovanniedwards.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1T78qAI79rT8PAongDfe8rXuFwO-gCIL94KRP5X47IpI/edit?usp=sharing; Instagram: https://www.instagram.com/gioedwrds/</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Judah Esquivel</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>jesquivel@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 3) — Character Design / Storyboarding / 2D Animation</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://judah99.myportfolio.com/</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1KlhceCtb6s1dNViXdr6cHizH0cK_8eb5/edit?usp=sharing&amp;ouid=113679051043423213306&amp;rtpof=true&amp;sd=true; Instagram: https://www.instagram.com/judah.99/</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Yuhan Feng</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>yuhanfeng@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 3) — Visual Development, Background Design / Independent Filmmaking / 2D Animation</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://gang0704.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1oMFLj31ejINDosSFe1SZzuSqJiz2WniJqWSiOsxiftU/edit?usp=drive_link</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>George Geng</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>georgegeng@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 3) — CG Modeling, Rigging, Texturing / CG Animation / Game Design</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://jorjboi.github.io/</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1LN1yw9V79w92PKsvOvaAWXJIX0vlkmzAaIyfOTgalWc/edit?usp=sharing</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Adriana Gonzalez</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>adrianagonzalez@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 3) — Visual Development, Background Design / Character Design / Prop Design</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://adrianagonzalezportfolio.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1nE-p36OPnki_IPOOEkxrLZZtVyWRAgmlR6lmGAlc1-4/edit?usp=drivesdk; Instagram: https://www.instagram.com/lemokki_</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Annie Han</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>anniehan@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 3) — Storyboarding</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://anniehanart.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/173hpAx5V8TarUnDxkOITsE2cGc0cOUalu6rr9QkTw5o/edit?tab=t.0; Instagram: https://www.instagram.com/anniehannibal/; LinkedIn: https://www.linkedin.com/in/annie-q-han/</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Kisoh Horie</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>kisohhorie@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 3) — Storyboarding / Illustration, Comics</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://kisohhorie.myportfolio.com/</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1JzvJd0ErcZbVcsXh5bbVxIWPA236OAbj8Zk79DPggsk/edit?usp=sharing; Instagram: https://www.instagram.com/kisohhorie/</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Erin Jiang</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>huilinjiang@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 3) — Color Design / Storyboarding / Illustration, Comics</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://huilinjiang.wixsite.com/erinjiang</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/10Wx3Nl9M5p8IPmTQvbUAyXHVe0687yrd2rJ3vXTou0s/edit?usp=drivesdk; Instagram: https://www.instagram.com/erinireri</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Kabir Kukathas</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>kabirkukathas@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 3) — 2D Animation / CG Animation / Character Design</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://kabirkukathas.myportfolio.com/</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/13x9ghtIsjFQ0mO3No7QHaS6lvmz4-gsEaUaZ1Wr9OMs/edit?tab=t.0; Instagram: https://www.instagram.com/kubbabeer/; Youtube: https://www.youtube.com/@kubbabeer</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Jiyoung Lee</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>jiyounglee@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 3) — Visual Development, Background Design / Character Design</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://jiyoungleeart.weebly.com</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1F91VmN6JjTBt0-11amhZSqSZX2JSMLfCgvrWa4RPPBs/edit?tab=t.0; Instagram: https://www.instagram.com/jizero_423; Youtube: http://www.youtube.com/@JiyoungLee-j7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Matthew Lei</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>mlei@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 3) — Storyboarding / Independent Filmmaking</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://matthewlei.com/</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1VD6JdyE-SBA52g6i_UtTPPggHKcrppe1lGyWUh4qDs4/edit?tab=t.s8hqsfwvk0py; Instagram: https://www.instagram.com/lei_doodles/; Youtube: https://www.youtube.com/@lei_doodles</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Zimeng Li</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>zimengli@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 3) — Visual Development, Background Design / Character Design / Color Design</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>https://zimengli.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1xeRRj27OzwUFwoqa9-_iq2KGKxqrXIPLMGtvAjRvdRk/edit?usp=sharing; Instagram: https://www.instagram.com/arya_doubleducks</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Stella Lukman</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>stellalukman@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 3) — 2D Animation / Character Design / Teaching, Education</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>http://www.stellalukman.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1ujxecx8oQXVsejBpMTCX5EcIs9RPVw1uiuPDb7eEUeY/edit?usp=sharing; Instagram: https://www.instagram.com/stellalukman; LinkedIn: https://www.linkedin.com/in/stella-lukman</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Jackie Manke</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>jackiemanke@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 3) — Character Design</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>https://jmmanke7.wixsite.com/jackie-m-portfolio</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1LVETUUXL2T9tBVk2JFdcV-8uON5ah-SE7Ip6ozxPO-k/edit?usp=sharing; Instagram: https://www.instagram.com/meearu_</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Lulu Mckown</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>lulumckown@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 3) — Character Design / Visual Development, Background Design / Independent Filmmaking</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>https://lulumckown.com/</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1BvU0s3M3wITkoZdJZi4BRmeymoxPn8bV2aP9fi_gFOc/edit?usp=sharing; Instagram: http://instagram.com/lulumckown; Youtube: https://www.youtube.com/@lulumckown</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Abby Mills</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>abbymills@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 3) — Independent Filmmaking / Character Design</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>https://agmillsart.com/</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1DjPEVKVBaZuZ5BWFvnnpwkx6iHwno3v2_bTv0ialaQw/</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Mateen Nassirpour</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>mateennassirpour@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 3) — Storyboarding / 2D Animation / Writing for Animation</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>https://mateennassirpour.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1GuJiNVatBRTF9HFMXeLTlCcIiyeLbU9hicZegnut7Wc/edit?usp=sharing; Instagram: https://www.instagram.com/lightningmateen_/</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Izzy Obey</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>izzyobey@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 3) — Illustration, Comics / 2D Animation / Independent Filmmaking</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>https://www.izby.work</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1lqpktIgAf_DaYut9I95dSY8HrzfGIgZgSi1_2TmhEak/edit?usp=sharing; Instagram: https://www.instagram.com/izbybun/; Youtube: https://www.youtube.com/@izbybun/videos</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Yunqing Pan</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>ypan@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 3) — Storyboarding / Illustration, Comics</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>https://yunqingpan.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1zrxfyvviGlsAxMb_tmu6kmyUC61s-d659K7gNEFoti4/edit?pli=1&amp;tab=t.0; Instagram: https://www.instagram.com/sallypan2022/; Youtube: https://www.youtube.com/@SallyPanArt</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Reni Park</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>laurenpark@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 3) — Storyboarding</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>https://renipark.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/11I2o9XB2K24NwvR92_rBzKsykvcIiL-SfsGqeuuMmFg/edit?tab=t.0#heading=h.hsevc1apatc8; Instagram: https://www.instagram.com/rosy.renirooo/; Youtube: https://www.youtube.com/@Renirooo</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Vincent Parkes</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>vincentparkes@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 3) — Independent Filmmaking / 2D Animation</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>https://vincentparkes.myportfolio.com/home</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1A9_33NfTOGyoHnIBHhhBESSLccTxj5e6ZgtYUJoAXW0/edit?tab=t.0; LinkedIn: http://www.linkedin.com/in/vincent-parkes-2a5b22291; Youtube: https://www.youtube.com/@Vincophia</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Diego Pimentel</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>diegopimentel@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 3) — Character Design / Visual Development, Background Design</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>https://diegopimentel3.wixsite.com/diego-pimentel</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/16bO3LzfoBY8RQv-oSlVZFhcp9Y1pJaY5SFQ0D4v4w9M/edit?usp=sharing; Instagram: https://www.instagram.com/diego.d.pimentel/</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Haiqing Qi</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>haiqingqi@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 3) — 2D Animation / Character Design / Independent Filmmaking</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>https://haiqingqi.myportfolio.com</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1m_2p6IalDveeeoKtyVjis9U8rIZIlimrfZTfqah36yY/edit?usp=drivesdk; Instagram: https://www.instagram.com/haiqing_qi; Youtube: https://www.youtube.com/@haiqingqi1810</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Haya Rasoul</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>hayarasoul@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 3) — Visual Development, Background Design / Content Creation for Social Media / Illustration, Comics</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>https://hayarasoul.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1-68YsS-KcZrX74enREwxNAfc8xk3Yt08TCGdCHdaZ_E/edit?usp=drive_link; Instagram: https://www.instagram.com/hayarasoul/</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Hsin-Kai (Kyle) Shao</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>kyleshao@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 3) — Storyboarding / Character Design</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>https://kyle-shao.web.app/works/index.html</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1ZLoypvRgdNqFaBNs2a9RoAa4hvom_HqFLjbnnSFkmYM/edit?usp=sharing; Instagram: https://www.instagram.com/kairruuu_/</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Jason Stephen</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>jasonstephen@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 3) — Visual Development, Background Design / Prop Design / 2D Animation</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>https://jasonstephenart.wixsite.com/portfolio</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1Dx4lP359sRJrfgS6B7YpR-x91pBMTUZXobKK-XYyo9E/edit?usp=sharing; Instagram: https://www.instagram.com/jsn_illust/; Youtube: https://www.youtube.com/@jsn_illust</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Yvonne Su</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>yiwensu@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 3) — Visual Development, Background Design / Character Design / Illustration, Comics</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>https://yvonnesu.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1DtKa4MS2-1Imxkudi21C_95hcgfPRpg-4fgp3f3BoIE/edit?usp=drivesdk; Instagram: https://www.instagram.com/fluviusy; Youtube: https://www.youtube.com/@Fluviusy/videos</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Sophia Uy</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>sophiauy@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 3) — Storyboarding / Independent Filmmaking / Illustration, Comics</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>https://sophiauy.myportfolio.com</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1_aaue8_xcdh4-wKGA4VyK5qYK6WDDj-8dC-EUs-5xgg/edit?tab=t.0; Instagram: https://www.instagram.com/soapitaro; Youtube: https://www.youtube.com/@soapitaro/videos</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Aniya Washington</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>aniyawashington@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 3) — Storyboarding / Illustration, Comics / Visual Development, Background Design</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>https://poiiquib.squarespace.com/</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1179lVCBOgRozSas_4QckDDT2fJQz3gfoLHZwS3wbYSQ/edit?usp=sharing; Instagram: https://www.instagram.com/poiiquib</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Val Yu</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>valerieyu@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 3) — Character Design / Visual Development, Background Design / Prop Design</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>https://valyuart.com/</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1dFGJC43Oko2nVnEG5ZkjGScO_BD-ps7_bofE-KMcdJc/edit?usp=sharing; Instagram: https://www.instagram.com/valexanderr</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Daixuan Yuan</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>daixuanyuan@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 3) — Visual Development, Background Design / Illustration, Comics / Character Design</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>https://daixuanyuan.myportfolio.com/</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1qqTyqtb5ogUW6haBojnjtXVdt7rPLJAr7rbMQDwNgTQ/edit?usp=sharing</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Sheryl Zhang</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>sherylzhang@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 3) — Independent Filmmaking / Character Design / Storyboarding</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>https://sherylzhang.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1-2iyROo5N1fKhYXoZqz7kgvwBHw3Lfzy2bt1tH55TYM/edit?usp=drivesdk; Instagram: https://www.instagram.com/sher0lz/; Youtube: https://www.youtube.com/@sherylzhang216</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Alyssa Anderson</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>alyssaanderson@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 4) — 2D Animation / Character Design / Illustration, Comics</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>https://alysstify.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1Vfb3cvZsRYUyrSDalc7474gg1maqG5G7q-Tkjy5FFx4/edit?tab=t.0; Instagram: https://www.instagram.com/alysstify/; Youtube: https://www.youtube.com/@alysstify/videos</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Nik Argos</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>nikolsargsyan@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 4) — Visual Development, Background Design / Storyboarding</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>http://nikolargos.myportfolio.com</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1rfUqxwMOQx7ZXoRUQCuPTXuJQ_m4Y5Pg/edit?usp=sharing&amp;ouid=104087287366470265651&amp;rtpof=true&amp;sd=true; Instagram: https://www.instagram.com/prowl.q/</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Emi Baumgardner</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>emibaumgardner@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 4) — Storyboarding / Independent Filmmaking / Writing for Animation</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>https://www.emi-baumgardner.com/</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1Zb0XVJ5m6BqWEND6r-KTwwX_ezvgb57w3njnbzvm0-I/edit?usp=sharing; Instagram: https://www.instagram.com/emgardnerart/; Youtube: https://www.youtube.com/@emgardnerart</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Marissa Brennan</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>marissabrennan@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 4) — Character Design / Color Design / Independent Filmmaking</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>https://marissabrennan.myportfolio.com</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1b_wndb8P0iroxDYpak0ZZWx0mhvnLSeUXqXsoFlHLS8/edit?usp=drivesdk; Instagram: https://www.instagram.com/mavzip</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Jamie Chin</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>yujiehchin@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 4) — Character Design / Visual Development, Background Design / Prop Design</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>https://www.yujiehchin.com</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1pofiHHV0U2-1Rt5d-F82b4AB8Q-xyTPpOH1eFrIMtKY/edit?usp=sharing; Instagram: https://www.instagram.com/xinyis_art_account/</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Hannah Coan</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>hcoan4@gmail.com</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 4) — 2D Animation / Storyboarding / Production Management, Recruiting</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>https://sites.google.com/view/hannahcoanportfolio/animation</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/10HryjXPCkDCVKeLsFd9wPJL5cSiTU0cUbj_b3aAzU-w/edit?usp=sharing; Instagram: https://www.instagram.com/viverran</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Antoine Couttolenc</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>antoinecouttolenccamacho@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 4) — Character Design / Visual Development, Background Design / Illustration, Comics</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>https://antoinecouttolenc.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/16okvDWH9FQCC-4Ge3Nsh5NhPySG3t9jJ/edit?usp=sharing&amp;ouid=116584942171699138122&amp;rtpof=true&amp;sd=true; Instagram: https://www.instagram.com/ant1.draws</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Chun Kit Fong</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>chunkitfong@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 4) — Illustration, Comics / Visual Development, Background Design / Storyboarding</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>https://chunkitfong.myportfolio.com/</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/161y3B3xGQCDmxQykli7v4T3dMJd2Cw7i11TgreMOAUY/edit?usp=sharing; Instagram: https://www.instagram.com/ckuuart/</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Valentine Guillemet</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>vyangyang01@gmail.com</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 4) — Illustration, Comics / Visual Development, Background Design / 2D Animation</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>https://valentineguillemet.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1vvXFvpiE2SHyDQYlbU1y_fXv9BU1lfU3C3Vr3e5Zaw0/edit?usp=sharing; Instagram: https://www.instagram.com/greenvalentiine</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Demian Guzman</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>demianguzman@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 4) — 2D Animation / Storyboarding / Illustration, Comics</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>https://www.demianguzman.com</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1kj9jIz8y6wPZ3w9KWyW4RvREZ-NGbrjiQmVXPWR2Eo4/edit?usp=sharing; Instagram: https://www.instagram.com/sr_rayones; Youtube: https://www.youtube.com/@sr_rayones5008/videos</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Jessica Ji</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>jessicaji@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 4) — Visual Development, Background Design / Character Design</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>https://jessicaji.myportfolio.com/</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1-BlPwNrPIVxYqXi2_wVwldTOtWKoARzsWOB6duYv_aE/edit?usp=drivesdk; Instagram: https://www.instagram.com/jessietr0n/</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Diya Joseph</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>diyajoseph@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 4) — Storyboarding / Writing for Animation</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>https://diyajoseph.weebly.com</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1EApHLIUxJ9ttDuFSyPGA67MAkEanqj3E0X4c1RnWN3Q/edit?usp=drivesdk; Instagram: https://www.instagram.com/pemqin; Youtube: https://www.youtube.com/@diya.joseph</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Ayla Kasimova</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>aylakasimova@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 4) — Visual Development, Background Design / Character Design / Color Design</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>https://aylakasimovabf54.myportfolio.com/work</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1qxTeG-5abIh26lfuX_ylukEgsrkFgKyVUl41C6lyIjk/edit?usp=sharing; Instagram: https://www.instagram.com/kasiliko/</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Ben Knight</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>benknight@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 4) — 2D Animation / Storyboarding / CG Animation</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>https://benknightowl.com/</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1CulfUjJ-CYeInJr83qUKEXoBGTmLfWw5MutTGXiictY/edit?usp=sharing; Instagram: https://www.instagram.com/knightowl_art/; Youtube: https://www.youtube.com/@KnightOwl_Art/videos</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Sofia Kondrasheva</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>sonyakondrasheva@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 4) — Character Design / Visual Development, Background Design / Storyboarding</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>https://oblacat.cargo.site/</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1-1v0pKFq3I0Td6w07AQFL80XMbZORNUGr8yqre6bGb0/edit?usp=drivesdk; Instagram: https://www.instagram.com/_oblacat_; Youtube: https://www.youtube.com/@oblacat_/featured</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Kalynn Lam</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>kalynnlam@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 4) — Visual Development, Background Design / Illustration, Comics / Prop Design</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>https://kalynnlam.com/visual-development</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1v65LxOCH306pGuWTK6rk3UDQGcmyrPrh0OQsmComSa8/edit?usp=sharing; Instagram: https://www.instagram.com/kalouriis/; LinkedIn: https://www.linkedin.com/in/kalynn-lam-886363266/</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Luke Lee</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>lukelee@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 4) — Storyboarding / 2D Animation</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>https://lukeleeportfolio.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1ZM2Qocq6xdbOUiR2MH8Oands8Rf--L3dQFODuaBHlYs/edit?usp=sharing; Instagram: https://www.instagram.com/binsoo.lee; Youtube: https://www.youtube.com/@binsoolee/videos</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Si Yi Lee</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>siyilee@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 4) — Storyboarding / 2D Animation</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>https://siyi-lee.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1sGFUGHvltnIrHWhBI9ppsDvrGEST2-tQ/edit?usp=sharing&amp;ouid=100286388431822044903&amp;rtpof=true&amp;sd=true; Instagram: https://www.instagram.com/saraileesiyi/; Youtube: https://www.youtube.com/@saraileesiyi</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Veda Lee</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>vedalee@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 4) — Independent Filmmaking / Illustration, Comics / Content Creation for Social Media</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>https://www.sakuraopal.com/</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/17AbnYQs6wnHktxC_PP6XG9_tdIACh5ZYSABzne8qCcQ/edit?usp=sharing; Instagram: https://www.instagram.com/sakuraopal/; Youtube: http://youtube.com/c/sakuraopalart</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Iris Li</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>irisli@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 4) — Storyboarding / Visual Development, Background Design</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>https://irisliportfolio.weebly.com</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1sIQnivO89NUHKNEfOk33vxtmU4NyDNJfATrDjg99ixY/edit?usp=drivesdk; Instagram: https://www.instagram.com/saltyfish_ii</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Mingyang Li</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>mingyangli@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 4) — Visual Development, Background Design / Illustration, Comics / Storyboarding</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>https://mingyangli.myportfolio.com/</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/11B_559elXmo6SjokebOzNsJ_TiHxC1sUTW_jKj0M33c/edit?usp=sharing</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Yuhan Liu</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>yuhanliu@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 4) — Storyboarding / Teaching, Education / 2D Animation</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>https://yuhanliustory.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1pvD8qHiA5S3tsAoFpt18StwxTeSps7PK/edit?usp=sharing&amp;ouid=105233666976924487441&amp;rtpof=true&amp;sd=true; Instagram: https://www.instagram.com/yuhanart_/; Vimeo: https://vimeo.com/user161378113</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Adriana Lopez Escalante</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>adrianalopez@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 4) — Visual Development, Background Design / Storyboarding / Character Design</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>https://adrianalopez.myportfolio.com/</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1OIA_5Hk3t2qkxoMG5tgAHPS2LNzeG53xkrYvVwMu5_Y/edit?usp=sharing; Instagram: https://www.instagram.com/adrxwberri/; Youtube: https://www.youtube.com/@adrxwberri/videos</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Amara Mancia</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>amaramancia@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 4) — Production Management, Recruiting / Storyboarding / Writing for Animation</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>http://amarasm.myportfolio.com</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1gF1elqZA3p0ug0wPs-v4-CnbzeicJRwfxgVRZbWuk1M/edit?usp=sharing</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Joyanne Marquetant</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>joyannemarquetant@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 4) — Character Design / Visual Development, Background Design / Color Design</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>https://joyannemarq.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1c0BY32ldlukv9KZluY4oslrxhelsORknqZPGZ0jQ4Bs/edit?usp=sharing; Instagram: https://www.instagram.com/joyannyy/</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Lillia Mueller</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>lilliamueller@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 4) — Visual Development, Background Design / Character Design / Prop Design</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>https://lilliamueller.myportfolio.com/</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1-44Y3z9Zg3z740fOjOFqD8wYFr3XpXatGQZLNvrcx_8/edit?usp=drivesdk; Instagram: https://www.instagram.com/leqwak</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Yenni Myung</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>yennimyung@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 4) — Storyboarding / Illustration, Comics / Character Design</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>https://yennimyung.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1JJIERuHXskEyNOgI31v7b2y6NaiF2denbt5svHi6gqE/edit?usp=sharing; Instagram: https://www.instagram.com/myunine_/</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Sihan Ning</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>cynthianing@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 4) — Visual Development, Background Design / Game Design / Color Design</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>https://sihanning.myportfolio.com/</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1dpZVsc2izt_IVNUBPXgIjeiQCFk73P7Y/edit?usp=drivesdk&amp;ouid=105109249923052750510&amp;rtpof=true&amp;sd=true; Instagram: https://www.instagram.com/whitecatjz</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Kiran Patel</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>kiranpatel@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 4) — Character Design / Illustration, Comics / Visual Development, Background Design</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>https://kiironch.squarespace.com/</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1ely5j2sg7Nxjvvyz17lwk9XSJU8fbh8NTf3juStisS4/edit?tab=t.0; Instagram: https://www.instagram.com/kiironch; LinkedIn: https://www.linkedin.com/in/kiran-patel-812576203/</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Nataël Renault</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>natael.renault@gmail.com</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 4) — Visual Development, Background Design / Illustration, Comics / 2D Animation</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>https://nataelrenault.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1bU_4O7iCC8yGkxMS4maQ7LMdwMdg-6l7NxPOGarPOE4/edit?usp=sharing; Instagram: https://www.instagram.com/hhfidelity</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Erika Salazar</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>erikasalazar@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 4) — Storyboarding / Character Design / Independent Filmmaking</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>https://erikakiseki.wixsite.com/theerikasalazar</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1CDwOroHj6_ENMn3L-LW244oGmaxpTLbe-vA3RVpDpNg/edit?usp=drivesdk; Instagram: https://www.instagram.com/theerikasalazar; Youtube: https://www.youtube.com/@ErikaKiseki/videos</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Haley Stemmons</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>haleystemmons@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 4) — 2D Animation / Visual Development, Background Design / Independent Filmmaking</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>https://haleystemmons.wixsite.com/portfolio</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/109pQQe3f6w2cb7z0_aeGcw6FegO1cSQjtkfT_Xo-hPE/edit?usp=drivesdk; Instagram: https://www.instagram.com/stemms_s; Youtube: https://www.youtube.com/@stemms</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Caro Vasquez</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>carolinevasquez@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 4) — Storyboarding / Character Design / 2D Animation</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>https://carovasquez.myportfolio.com</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1DailNI36Oq3tMZw_c912vgwF35d3GK6vCHiVfjbOMVk/edit?usp=drivesdk; Instagram: https://www.instagram.com/graiisonz</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Siyu Wang</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>siyuwang@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 4) — Character Design / Visual Development, Background Design / Game Design</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>https://siyuwang764d.myportfolio.com</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/15ZvsXt72U3xx1SR2knxvJowk736jLNDZ/edit?usp=drivesdk&amp;ouid=104120131169371429149&amp;rtpof=true&amp;sd=true; Instagram: https://www.instagram.com/seafridge_eeee</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Zechen Wang</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>zechenwang@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 4) — Storyboarding / 2D Animation / Independent Filmmaking</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>https://zechenwang.myportfolio.com/</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/18HN6POpoSpXAHt_p69eumH92BiYhWzg8RuPVK1PAkrA/edit; Instagram: https://www.instagram.com/zechen_conner_wang</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Yuecheng Wei</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>yuechengwei@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 4) — Character Design / Illustration, Comics / Visual Development, Background Design</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>https://www.aidanweiart.com/</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Resume: https://drive.google.com/drive/folders/11EUdonoR9Uy9Oeg5Zeywa5ydWLHt4Fql?usp=sharing</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Christina Wu</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>christinawu@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 4) — Character Design / Independent Filmmaking / Illustration, Comics</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>https://christinawu.myportfolio.com/films-1</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1ywgCGNOsICCN8xbi9RzW9FsGba6-H6-fa_UBanaEnIw/edit?usp=sharing; Instagram: https://www.instagram.com/wwuhoo; Youtube: https://www.youtube.com/@wwuhoo/videos</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Awa Yin</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>yushanyin@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 4) — Character Design / Visual Development, Background Design / 2D Animation</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>https://yushanyin.wixsite.com/portfolio</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1cnhDMnOaCJUi9sOXbfFX8cVye0-VNva4IykQMqIbPvk/edit?usp=sharing; Instagram: https://www.instagram.com/isawa317/</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Huayi Yu</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>huayiyu@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 4) — Motion Design / Independent Filmmaking / Character Design</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>https://www.huayiyu.com/</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1ZEwENl54OVQhLTaIth5q55n86oG1bPHyciHJU_VAcFU/edit?usp=sharing; Instagram: https://www.instagram.com/huayi11/; Vimeo: https://vimeo.com/huayiyu</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Oz Zhang</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>ozzhang@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 4) — Visual Development, Background Design / Independent Filmmaking / Writing for Animation</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>https://ozzhang.myportfolio.com/</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1msJ2hQE2CDH26IQ2Iwb3BwNZ1402958DRi_CglFOpbA/edit?usp=sharing; Instagram: https://www.instagram.com/naiilao/; Youtube: https://www.youtube.com/@naiilao3518</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Esther Zhu</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>estherzhu@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Character Animation (BFA 4) — Visual Development, Background Design / Character Design / Illustration, Comics</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>https://disasterzoo.net</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1jLZIpm76ayOmhXIKQ2Fuq0XMSnXTGMglHrIFUkpJREk/edit?usp=sharing; Instagram: https://www.instagram.com/disasterzoo/</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Ignacio Anacona</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>ignacioanacona@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Character Animation (Affiliates) — Storyboarding / Visual Development, Background Design</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>https://ignacioanacona.com/portfolio/</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1uP6bwvIXg8h2QAf7KChZizsJMC4bb5oXVlROD0C1XNI/edit?usp=sharing; Instagram: https://www.instagram.com/nacioanacona/; Youtube: https://www.youtube.com/@nacioanacona</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Percy Banks</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>pbanks@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Character Animation (Affiliates) — Character Design</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>https://percybanks.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1JBCcCyA6B_CilGKSSHguLq6PqvNQ09Bu2mBV3o8rCEU/edit?usp=drivesdk; Instagram: https://www.instagram.com/perkadet; Youtube: https://www.youtube.com/@perkadet/videos</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Ava Bishop</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>abishop@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Character Animation (Affiliates) — Storyboarding / Character Design / 2D Animation</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>https://lilustration.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/12uqNv109fldtxiXxbQ7NwQZp8i09U_IUPDAeKtrglZo/edit?usp=drivesdk; Instagram: https://www.instagram.com/lilustrationgram/</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Kirsten Gaila</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>kirstengaila@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Character Animation (Affiliates) — Character Design / Visual Development, Background Design / Color Design</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>https://kirstengaila.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1AG1gqiJY770eutsuE4b0wVrVeSIr67DhpqZgbsR-JB4/edit?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Wasitee Hart</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>wasiteehart@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Character Animation (Affiliates) — Writing for Animation / Independent Filmmaking / Visual Development, Background Design</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>https://wasiteehart.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1v_X1jnstTsvzaS0IyECIVxHXfHKa10snXFsNC-biMy0/edit?usp=sharing; Instagram: https://www.instagram.com/wassart.tv/; Youtube: https://www.youtube.com/@wassart/videos</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Fia Johansson</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>sjohansson@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Character Animation (Affiliates) — Independent Filmmaking / Visual Development, Background Design / 2D Animation</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>https://fiajohansson.weebly.com</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1IrgifKtjvSyLOCtrd9VgNDxGzoj_OuVnaEw7hveJwzU/edit?usp=sharing; Instagram: https://www.instagram.com/redesert_sketches/</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Patrycja Kupczyk</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>patrycjakupczyk@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Character Animation (Affiliates) — Storyboarding / Visual Development, Background Design / Independent Filmmaking</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>https://patrycjakupczyk.com</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1DnYf4O33_n9SLcSKVtezO6mddBeuvl0BePm0QeKHmOc/edit?usp=sharing; Instagram: https://www.instagram.com/paatty.art/; Youtube: https://www.youtube.com/@paatty_art</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Lauren Spitzer</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Laurenspitzer@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Character Animation (Affiliates) — Visual Development, Background Design / Character Design</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>https://www.laurenspitzer.com/</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1b-DvapuEuyqxmn48vPWAg-lCxzBltPr7AgqMMjaEr_Q/edit?usp=sharing; Instagram: https://www.instagram.com/lojoysi/; LinkedIn: http://www.linkedin.com/in/lauren-spitzer-43b0752b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Julie Zheng</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>juliezheng@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Character Animation (Affiliates) — 2D Animation / Independent Filmmaking / Motion Design</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>https://juliezportfolio.cargo.site/</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1ApOzdGFCwQOzaUpRZxLK60Nqis2x-Cv9HJlSG3OfeGk/edit?tab=t.0; Instagram: https://www.instagram.com/julie_z._.z/; Vimeo: https://vimeo.com/user142448931</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Sydney Agans</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>syd.agans@gmail.com</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Character Animation (Recent Alumni) — Storyboarding / Writing for Animation / 2D Animation</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>https://sydneyagans.myportfolio.com/</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1TAasF76aq7bnZsAErfbFUkB89SyTCjfAnP8HG8mPOIw/edit?usp=sharing; Instagram: https://www.instagram.com/sydzdrawingz</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Colin Armistead</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>colinarmistead@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Character Animation (Recent Alumni) — Independent Filmmaking / 2D Animation / Character Design</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>https://www.colinarmistead.com/</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Resume: https://www.colinarmistead.com/uploads/1/1/8/3/118307840/armistead-colin-resume.pdf; Instagram: https://www.instagram.com/colinarmistead/</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Victoria Basadre</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>victoria.basadre@gmail.com</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Character Animation (Recent Alumni) — Independent Filmmaking / Storyboarding / Character Design</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>https://victoriabasadre.myportfolio.com/</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/10QkAcD0s1XLEt6Ht6G4AbdsWJsS77a7VcCpipnSemx4/edit; Instagram: https://instagram.com/vicbarts</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Emma Bliese</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>embliese.art@gmail.com</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Character Animation (Recent Alumni) — Writing for Animation / Storyboarding / Illustration, Comics</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>https://embliese.wixsite.com/portfolio</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1O14ITWeWHOKyJAmi5VFZiZcVrG78vLQv/edit?usp=sharing&amp;ouid=110613082126155277033&amp;rtpof=true&amp;sd=true; Instagram: https://www.instagram.com/em_breezy_/; Youtube: https://www.youtube.com/@em_breezy_/videos</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Amy Boisvert</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>amybanims@gmail.com</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Character Animation (Recent Alumni) — Storyboarding / Independent Filmmaking / Writing for Animation</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>https://amyboisvert.wixsite.com/amy-boisvert-story</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Resume: https://drive.google.com/file/d/1dqzyzScHcsJ9lqCQXBUeki-LggnQdSq1/view?usp=sharing; Instagram: https://www.instagram.com/bigboyamy/; Youtube: https://www.youtube.com/@bigboyamy/videos</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Asher Borison</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>asherborison@gmail.com</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Character Animation (Recent Alumni) — Storyboarding / Writing for Animation / Character Design</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>https://asherborison.com/</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1nf6dTLJRL2tnk4oa0lcjaAs_zgUDDVXgfxEutGQWOWY/edit?usp=sharing; Instagram: https://www.instagram.com/asher_borison/; Youtube: https://www.youtube.com/@asher_borison/videos</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Anya Butler</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>meppity@gmail.com</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Character Animation (Recent Alumni) — Content Creation for Social Media / Character Design / Prop Design</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>https://www.meppity.com</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1iNIRziu2Ikxb19f8gkyiEoZ-x2hZ0VyIKFHyFg7G3kI/edit?usp=sharing; Instagram: https://www.instagram.com/meppity; Youtube: https://www.youtube.com/c/meppity</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Mina Chacko</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>minachacko@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Character Animation (Recent Alumni) — Character Design</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>https://minachacko.myportfolio.com/</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1ABLTLAuYgMfxPgPbjXT0Sqx3dtwQWDCOWS_IOsQadwY/edit?tab=t.0; Instagram: https://www.instagram.com/kanicomics/; Youtube: https://www.youtube.com/@minac949/videos</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Thet Chal</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>thetchal.art@gmail.com</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Character Animation (Recent Alumni) — Compositing / CG Modeling, Rigging, Texturing / Visual Development, Background Design</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>https://thetchal.portfolio.site/</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1pVGXy2aaP0apbkPC36NDpXkh3vcNvp9z1C_l5zqY7LY/edit?usp=sharing; Instagram: https://www.instagram.com/tctakili/; Youtube: https://www.youtube.com/@tctakili</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Ares Cheng</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>arescheng@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Character Animation (Recent Alumni) — Character Design / Visual Development, Background Design / Illustration, Comics</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>https://areschengart.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1IDmZnsqKd24FH-t9nfG5g8GRmOR459-4tnkiM-dwSMs/edit?usp=sharing; Instagram: https://www.instagram.com/stormeris/</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Yunie Choi</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>choiyh2616@gmail.com</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Character Animation (Recent Alumni) — Character Design / Visual Development, Background Design / Illustration, Comics</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>https://yuniechoi.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1zWqvDF2o_E164c_3HmsD15N793um1EA6kCvheNW8GEw/edit?usp=sharing; Instagram: https://www.instagram.com/uni.ch_art/; Youtube: https://www.youtube.com/@YunieChoiArt</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Katharine Doescher</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>katharine.f.doescher@gmail.com</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Character Animation (Recent Alumni) — Character Design / 2D Animation / Game Design</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>https://katharinedoescher.myportfolio.com/character-design</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1HXKWj5w7x6AyAyogdzvUEvrvAmXKbbdV3hlQOVW47JU/edit?usp=drivesdk; Instagram: https://www.instagram.com/skatfay; Youtube: https://www.youtube.com/@katdoe4779/videos</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Tia Gilles</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>tdgilles@gmail.com</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Character Animation (Recent Alumni) — Storyboarding / Writing for Animation / Production Management, Recruiting</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>https://www.tiagilles.com/</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1WXv4-xUU_P5LsAzFImdlSLymRS9RKN1rz3aKNdnYFL8/edit?usp=sharing; Vimeo: https://vimeo.com/user97942166; Youtube: https://www.youtube.com/@tiagilles/videos</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Maria Jaramillo</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>mariajaramillo@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Character Animation (Recent Alumni) — Storyboarding</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>https://maria-jaramillo.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Resume: https://drive.google.com/file/d/19ynbduZ4grGH7H3h2FGTYJe93vQGCkEo/view?usp=sharing; Instagram: https://www.instagram.com/_jaramari_/; LinkedIn: https://www.linkedin.com/in/maria-jaramillo-0bb646205</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Wesley Joseph Prussing</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>noharmradio@gmail.com</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Character Animation (Recent Alumni) — Independent Filmmaking / Visual Development, Background Design / 2D Animation</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>https://noharmradio.com/</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/14cPaGCt3pKptsLcq4Yuvxyb5IStSGGWa1hB1wk1kzAI/edit?usp=sharing; Instagram: https://www.instagram.com/noharmradio/; Youtube: https://www.youtube.com/@noharmlive/videos</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>David Khan</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>danishkhan@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Character Animation (Recent Alumni) — Storyboarding / Character Design / Visual Development, Background Design</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>https://danishdavidkhan.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1idJK_2TmQIl62EuKnpJiLAL2pXNCqzKLb1NcGbKe2f8/edit?usp=sharing; Instagram: https://www.instagram.com/davidd.khan/; Youtube: https://www.youtube.com/@davidkhan9716</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Michelle Kuo</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>michellekuoart@gmail.com</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Character Animation (Recent Alumni) — Visual Development, Background Design / Illustration, Comics / Character Design</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>https://michellekuo.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1EtE5ndtvqq-fnzeXjoUwsKnZ3hLdsA0Tkc06a0eyHso/edit?usp=sharing; Instagram: https://www.instagram.com/mkuoart</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Leo Lashley</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>lashleyleo@gmail.com</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Character Animation (Recent Alumni) — 2D Animation / Storyboarding</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>https://leolashley.com/</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1vJqlqBQDiFz3cO7Zbq5AomL7_jPQWT1MwmCcBfJyjEw/edit?usp=sharing; Instagram: https://www.instagram.com/seawaveleo/; Youtube: https://www.youtube.com/seawaveleo</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Yang Liu</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>yangliu@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Character Animation (Recent Alumni) — 2D Animation / Visual Development, Background Design</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>https://nirvanayang.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Resume: https://drive.google.com/file/d/1wMNieN7k-hSJhq4pYmHoxE-Q71ZOCvuA/view?usp=sharing; Instagram: https://www.instagram.com/nirvanayang/; LinkedIn: https://www.linkedin.com/in/yang-liu-639034266/</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Gloria Lo</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>cl2gloria@gmail.com</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Character Animation (Recent Alumni) — Storyboarding / Illustration, Comics / Visual Development, Background Design</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>https://glorialoart.weebly.com</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1b-ifNIDTuKDbdEUx3igqq3xcruwdNdtKM8SdKB7awNU/edit?usp=sharing</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Tyra Ly</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>tyraly@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Character Animation (Recent Alumni) — Visual Development, Background Design / Color Design / Prop Design</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>https://lunely.cargo.site/</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1-IYSBaIiYM2pZIZ0lhxwQ0vNVoVjODI0NY2F9adpwpc/edit?usp=drivesdk; Instagram: https://www.instagram.com/clovercae/</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Isis Mejia-Duarte</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>isismejia32@gmail.com</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Character Animation (Recent Alumni) — Storyboarding / Visual Development, Background Design / Writing for Animation</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>https://isismejia.myportfolio.com/</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1vdEm9deBaD6P5JLGEr_wM1HlWKBMWfbwNF_reKu08Jw/edit?usp=drivesdk; Instagram: https://www.instagram.com/artmejia03</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Ryan Mesidor</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>ryanmesidor@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Character Animation (Recent Alumni) — Storyboarding / Color Design / Independent Filmmaking</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>http://www.ryanmesi.com</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1JfVePUTBvjHcM0UrQGn5b6XNvFk-reLhGnMb9DM0lIE/edit?usp=sharing; Instagram: https://www.instagram.com/ryoodraws/; Youtube: http://youtube.com/@ryoodraws/videos</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Clara Montalvo</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>blackpearl4516@gmail.com</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Character Animation (Recent Alumni) — Storyboarding / Visual Development, Background Design / Independent Filmmaking</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>http://www.claramontalvo.com/</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1l1OJO37nz9MdhiRiQ5vDw5qK_Tv5f79CW8KuaTEZa7I/edit?usp=sharing; Instagram: https://www.instagram.com/sugarmause/; Youtube: https://www.youtube.com/@sugarmause</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Pavit Panag</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>panagpavit@gmail.com</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Character Animation (Recent Alumni) — Visual Development, Background Design / Color Design / Character Design</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>https://pavitpanag.myportfolio.com/</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/11LiB7awjMD9NN8QeMl0ljbHgd39cAK9ltUu1m4RqDyw/edit?usp=drivesdk; Instagram: https://www.instagram.com/ciraleth; Youtube: https://www.youtube.com/@ciraleth/videos</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Grace Park</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>gracepark408@gmail.com</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Character Animation (Recent Alumni) — Storyboarding / Character Design / Teaching, Education</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>https://www.graceparkart.com</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1TooDTBhbMWNuNT7r_EWjMBlo0xU_6-P2Lkc0RppVbnk/edit?usp=sharing; Instagram: https://www.instagram.com/graceparkart/; LinkedIn: https://www.linkedin.com/in/graceparkart/</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Jaimi Qiu</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>jaimiqiu@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Character Animation (Recent Alumni) — Color Design / Compositing / Visual Development, Background Design</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>https://jaimiqiu.myportfolio.com/</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1peLZzrSqkBPwiXksjh5gkhSV2zwZZEZy-W13x3uA2h4/edit?usp=sharing; Instagram: https://www.instagram.com/owldreig/</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Claire Seckler Sun</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>clairesecki1002@gmail.com</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Character Animation (Recent Alumni) — Storyboarding / 2D Animation / Illustration, Comics</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>https://claireseckler.wixsite.com/clairesecklerportfol</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1A5OIiCfB8jsOpCOFmYJD365P35dl_hX8WgHwHq6q22Q/edit?usp=sharing; Instagram: https://www.instagram.com/claire_vik_seckler/; Youtube: https://www.youtube.com/@claireseckler7951</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Jennifer Shi</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>jennifer@chronoverse.org</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Character Animation (Recent Alumni) — Storyboarding / 2D Animation</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>https://eggifer.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1c7XTrWnYo-uf8VqmXUOHPi8jtd0829XD2OoDIlwZm24/edit?usp=sharing; Instagram: https://www.instagram.com/eggifer/; LinkedIn: https://www.linkedin.com/in/jennshi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Lewis Tarver</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>lewvvk@gmail.com</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Character Animation (Recent Alumni) — Independent Filmmaking / 2D Animation</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>https://lewvvk.com/</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1t5cE_0l7E6XDlnWo5BVvYLxXMMKL9gqtd0P8IlAVbAg/edit?usp=sharing; Instagram: https://www.instagram.com/lewvvk/; Youtube: https://www.youtube.com/@lewvvk</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Isac Urbina</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>ike.urbina@gmail.com</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Character Animation (Recent Alumni) — CG Modeling, Rigging, Texturing / Independent Filmmaking / Game Design</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>https://iturbina.art/</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Resume: https://drive.google.com/file/d/1FC0G8_O7lvh14hOwRUJiZsFEXZ7D9NJt/view?usp=share_link</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Skye Wang</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>skyewang0729@gmail.com</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Character Animation (Recent Alumni) — Motion Design / Production Management, Recruiting / Independent Filmmaking</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>https://skyewangart.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1pK-8WicZvbuI3XltdmiRsyjOz0Q0hBffd47fTT4JvYU/edit?usp=sharing</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Yao Xu</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>yaoxu03.art@gmail.com</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Character Animation (Recent Alumni) — Visual Development, Background Design / Illustration, Comics / Independent Filmmaking</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ya_0xu/</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1qLGEi2RzA8knUGzsJJAI0jr6N3cdRV-3/edit?usp=sharing&amp;ouid=103725006049263462401&amp;rtpof=true&amp;sd=true</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Ben Aitchison</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>benjaminaitchison@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Experimental Animation (BFA 1) — CG Modeling, Rigging, Texturing / 2D Animation / Illustration, Comics</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>https://benaitchison.com/</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/18Cv1_xeAKi1nAtes05rzfmHFnJ3_-uzlzhFuURXBkj0/edit?tab=t.0; Instagram: https://www.instagram.com/beni_aitchison</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>N Bommarito</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>nbommarito@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Experimental Animation (BFA 1) — Experimental Techniques / 2D Animation / Visual Development, Background Design</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>https://nbommarito.com/</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1leB-CvRKhyrvM5pP1wFhSXKYHyiiMZ2Lg67PdBdYLss/edit?usp=sharing; Instagram: https://www.instagram.com/jank.ant/</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Maria Kim</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>mariakim@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Experimental Animation (BFA 1) — Stop-Motion, Puppetry</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/drive/u/2/folders/1o40yas36JjKmkmhOzNwpZFViV3hKCn7W</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1TojPiC_5BTho2ib6MS5vKK4W8tLl07stJshn7Rc6Goc/edit?tab=t.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Sophie Tsai</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>sophietsai@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Experimental Animation (BFA 1) — Experimental Techniques / 2D Animation / Independent Filmmaking</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>https://soymillk.com/</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1-Y_xt_Izu90iis9aVydnl7xyefoDW9_O9PfnfkTF3jk/edit?usp=drivesdk; Instagram: https://www.instagram.com/gakkibear</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Elizabeth Albrecht</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>elizabethalbrecht@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Experimental Animation (BFA 2) — 2D Animation / Experimental Techniques / Stop-Motion, Puppetry</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>https://elizabethalbrecht.cargo.site</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1_J_uyiNhbKObbi-g2siBje9syZz_4Q9gPt1lLwcChNY/edit?usp=sharing; Instagram: https://www.instagram.com/elizabeth.wei.yun.albrecht/; Youtube: https://www.youtube.com/@ElizabethWeiYunAlbrecht</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Vincent Ochoa</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>vincentochoa@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Experimental Animation (BFA 2) — CG Animation / 2D Animation / Stop-Motion, Puppetry</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>https://vincentochoa6.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Resume: https://drive.google.com/file/d/14kH-H3LtBkzrboF8I0lbmmXAAbY7P6zi/view?usp=drivesdk; Instagram: https://www.instagram.com/rattkingg6</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Sophia Vietro</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>sophiavietro@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Experimental Animation (BFA 2) — Experimental Techniques / Independent Filmmaking / Stop-Motion, Puppetry</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>https://sophiavietro.com/home.html</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1oKYHnB1-BxQTiPJLVpX3NnWXrd08U-cH04i7c199bMg/edit?usp=sharing</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Mengshi Hu</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>mengshihu@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Experimental Animation (BFA 3) — Independent Filmmaking / CG Animation / Stop-Motion, Puppetry</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>https://humengshi.myportfolio.com</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1ZSUTuXI4tB3efzDAtU_I1klFKbnudgc3yaHzApHQMGY/edit?usp=sharing</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Piper Yuhe Jiang</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>piperjiang@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Experimental Animation (BFA 3) — Experimental Techniques / Visual Development, Background Design / CG Animation</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>https://piperyuhe.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Resume: https://drive.google.com/drive/folders/1TIEIA8_bEX1d2k3l8k64MKI4REaW1qju</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Olive Milford</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>olliemilford@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Experimental Animation (BFA 3) — Experimental Techniques / Stop-Motion, Puppetry / Immersive Media Art</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>https://www.olivemilford.org</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1qzO6mNuOTXrlKdufR42BexVBuHiohffBlz2sz4wFAVg/edit?tab=t.0; Instagram: https://www.instagram.com/angry.fae; Youtube: https://www.youtube.com/@angryfae</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Charlotte Sun</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>charlottesun@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Experimental Animation (BFA 3) — Experimental Techniques / 2D Animation / Character Design</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>https://charlottesunart.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1wnP18yrO_iFA4b6V67w88_3d1b6G7yTRGmG4kJDQVNQ/edit?usp=drive_link; Youtube: https://youtu.be/ohqiHFLVwSo</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Ella Rae Canonizado</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>ellacanonizado@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Experimental Animation (BFA 4) — Independent Filmmaking / Experimental Techniques / Stop-Motion, Puppetry</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>https://ecanon.myportfolio.com/</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1fWPdcs9kHht8R-GD0QxkgJ4T3W4MQj1mE5kkRWELMmU/edit?usp=sharing; Instagram: https://www.instagram.com/fuddleskin; Youtube: https://www.youtube.com/@ellarae1566</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Erin Chao</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>erinchao@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Experimental Animation (BFA 4) — Stop-Motion, Puppetry / Illustration, Comics / Experimental Techniques</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>https://erinchao.myportfolio.com/</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1IPt0qp7wKsTyfuOAePhzn_lLGuDoWMtuW7ajlhZV_3I/edit?usp=sharing; Instagram: https://www.instagram.com/3rincha0</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Luc Duggan</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>lucieduggan@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Experimental Animation (BFA 4) — Experimental Techniques / 2D Animation / Stop-Motion, Puppetry</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>https://lucduggan.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1HQbF4GYcdJ1bWCjRr9Mb-YN0HPcUxTVrp5VMhurqjQg/edit?usp=sharing; Instagram: https://www.instagram.com/_leeseel_/; Youtube: https://www.youtube.com/@_leeseel_/videos</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Eva Goldfinger Scalzo</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>evagoldfingerscalzo@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Experimental Animation (BFA 4) — Experimental Techniques / Visual Development, Background Design / Stop-Motion, Puppetry</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>https://evagoldfingerscalzo.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1Lgpbtho3qhIh0VKfqs-nePiCChScQ3KC3vYbljy69PY/edit?usp=drivesdk; Instagram: https://www.instagram.com/friyedeg/</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Edie Harper</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>edieharper@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Experimental Animation (BFA 4) — Stop-Motion, Puppetry / Character Design / 2D Animation</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>https://www.edielucille.com/</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1IrTsg3HmALtHHAeiwnnt_kTAzMC8SFm5BrEX98OHi38/edit?usp=drivesdk; Instagram: https://www.instagram.com/storkdoesart; Youtube: https://www.youtube.com/@edieanimates</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Daun Jeong</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>daunjeong@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Experimental Animation (BFA 4) — Experimental Techniques / Prop Design / Character Design</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>https://daunjeong2.wixsite.com/mysite/portfolio</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1uwuulz0KYoRSFZU9ymZ5RLpbKnPdz80HXaIyY4kdMxA/edit?usp=sharing; Instagram: https://www.instagram.com/nuadgnoej/</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Jeongeun Lee</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>jeongeunlee@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Experimental Animation (BFA 4) — CG Modeling, Rigging, Texturing / CG Animation / Teaching, Education</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>https://ellielee.site/</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Resume: https://drive.google.com/file/d/1hsCItXwA7IipbSH9gtaICOhP2SvZSs-u/view?usp=sharing; Youtube: https://www.youtube.com/@JeongeunLee-kk7ds</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Averi Roes-Kern</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>averiroeskern@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Experimental Animation (BFA 4) — Experimental Techniques / Independent Filmmaking / Stop-Motion, Puppetry</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>https://averiroeskern.weebly.com/</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1G1dAIb1T552lhV3jsmYwm7vGNxWrEl7iayCBnKmxiHQ/edit?usp=sharing; Instagram: https://www.instagram.com/lychenthropy/; Youtube: https://www.youtube.com/@lychenthropy/videos</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Ignacio Sandoval-Reilly</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>elreilly@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Experimental Animation (BFA 4) — Stop-Motion, Puppetry / 2D Animation / Illustration, Comics</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>https://www.moonneca.com/</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr"/>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1XsRinqbLA9_0SoERyhHF2nzQUAcZ308Hr6X0rKl28ck/edit?usp=sharing; Instagram: https://www.instagram.com/moonneca/; Youtube: https://www.youtube.com/@Mooneco/videos</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Adrian Francisco Almaraz Guajardo</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>adrianalmaraz@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Experimental Animation (MFA 1) — 2D Animation / Illustration, Comics / Experimental Techniques</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>https://adrianalmarazportfolio.com/</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1qJm50cAgdDXGPh8v4e0D1NnFPU7cZaDVaScgunPS-sY/edit?usp=sharing; Instagram: https://www.instagram.com/adrianalmaraz24/</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Diego Cumplido</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>diegocumplido@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Experimental Animation (MFA 1) — Character Design / Writing for Animation / Experimental Techniques</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1FRoV3MfqQrQfIEy6hApWM0REemmAqGxr/view?usp=sharing</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Resume: https://drive.google.com/file/d/1uX6SguL4JpuqopmmsmRDWHI3jT_FkM8r/view?usp=sharing; Instagram: https://www.instagram.com/diegocumplidocomics</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Shuyuan Deng</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>shuyuandeng@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Experimental Animation (MFA 1) — 2D Animation / CG Modeling, Rigging, Texturing / Stop-Motion, Puppetry</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr"/>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>https://www.dsyart.com</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1HK30xC2BW0ItI-ePEGvMmcD2qVuM6TJ2NiNeqn7nvak/edit?tab=t.0; Youtube: https://www.youtube.com/@shuyuandeng1115/videos</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>J.K. Kim</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>jkkim@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Experimental Animation (MFA 1) — Character Design / Stop-Motion, Puppetry / Independent Filmmaking</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>https://jkkim.myportfolio.com/</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr"/>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1XmqMOd1vzMa5LpnWhmqSLTzq-4SiZKUtI7vLgg_2Hbw/edit?tab=t.0; Instagram: https://www.instagram.com/jinkyeoungkim; Youtube: https://www.youtube.com/@J.K_Kim/videos</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Zechen Li</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>lzli@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Experimental Animation (MFA 1) — 2D Animation / Visual Development, Background Design / Experimental Techniques</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr"/>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>https://zechenli.com/</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1aop7AIXd-N1cS7YJtG8cwjpneArg8vCtqTrari6Qd0s/edit?usp=sharing; Instagram: https://www.instagram.com/lukyaezc/; Vimeo: https://vimeo.com/zechenli</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Huei Ming Lim</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>hueilim@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Experimental Animation (MFA 1) — 2D Animation / Experimental Techniques / Writing for Animation</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr"/>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>https://hueiming19.wixstudio.com/portfolio</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1rJ89ACVosEZ_3NErWSSIlJGtGMwJ3kgChBjQlB8KuDU/edit?usp=sharing; Instagram: https://www.instagram.com/hueiming_lim_animation</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Jiajing Ling</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>jiajingling@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Experimental Animation (MFA 1) — 2D Animation / Illustration, Comics / Teaching, Education</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr"/>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>https://jiajingling0.com</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr"/>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Resume: https://drive.google.com/drive/folders/1DqEZ9NlhXLkGGno2mizzQ088gjqO-e3D?usp=drive_link</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Ana Sofía Navia López</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>anasofianavialopez@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Experimental Animation (MFA 1) — 2D Animation / Illustration, Comics / Experimental Techniques</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr"/>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>https://anasnavia.com/</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr"/>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Resume: https://drive.google.com/file/d/17-SK9GQvehpapPoegg_sReVTGyl2ENGo/view?usp=sharing; Instagram: https://www.instagram.com/anasnavia</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Lu Ren</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>luren@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Experimental Animation (MFA 1) — 2D Animation / Experimental Techniques</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr"/>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>https://renllu.cn/</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr"/>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Resume: https://drive.google.com/file/d/1wuUXWh7L-lKGYevr9Xe9AgJzKf0jyI8h/view?usp=sharing; Instagram: https://www.instagram.com/almondtea7/; Youtube: https://www.youtube.com/@LuREN-eacn</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Sarah Ruyle</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>rueruyle@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Experimental Animation (MFA 1) — 2D Animation / Illustration, Comics / Experimental Techniques</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr"/>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>https://walkingfish.neocities.org/</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr"/>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Resume: https://drive.google.com/file/d/1etVvhTtVftiS3AaH6UmirvhJ88Cz8QZh/view?usp=sharing; Instagram: https://www.instagram.com/w4lkingfish/; Youtube: https://www.youtube.com/@w4lkingfish</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Ruiting (Tina) Guo</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>tinaguo@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Experimental Animation (MFA 2) — 2D Animation / Content Creation for Social Media / Visual Development, Background Design</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>https://rguoaaa3.myportfolio.com/</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr"/>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1M_QSESbqpBhXlUqcnWJQo_ip5u3C16H6x60773kxiNw/edit?usp=sharing; LinkedIn: https://www.linkedin.com/in/ruiting-tina-guo-91bb62174/</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Vivian Kong</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>viviankong@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Experimental Animation (MFA 2) — Stop-Motion, Puppetry / Independent Filmmaking / Production Management, Recruiting</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>https://viviankong.myportfolio.com</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr"/>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>Resume: https://drive.google.com/file/d/1_kO8Q5h0c_3L2DWCK9LgdQ1UcwTP4TwA/view?usp=sharing; Instagram: https://www.instagram.com/kong.artchive/</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Stella Lee</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>stellalee@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Experimental Animation (MFA 2) — CG Modeling, Rigging, Texturing / Experimental Techniques / Content Creation for Social Media</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr"/>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>https://seung-hyun-lee.com/</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr"/>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1zvqq7Zp14Lzwu3KOMAraTqQh6UUqAD7zOyWb7ivcxLs/edit?usp=sharing; Instagram: https://www.instagram.com/outliersvision/</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Deni Martha Lopez</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>denimarthalopezdellamarytello@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Experimental Animation (MFA 2) — Teaching, Education / Experimental Techniques / Independent Filmmaking</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr"/>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>https://denimarthalopez.myportfolio.com/</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr"/>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1lzUu_u8sDFFMLzj8cwH-1nUsWS7b9qgMQNmuUFOhkM4/edit?usp=sharing; Vimeo: https://vimeo.com/malvibrada</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Olivia Porrill</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>oliviaporrill@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Experimental Animation (MFA 2) — 2D Animation / Visual Development, Background Design / Illustration, Comics</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>https://oliviaporrilla54c.myportfolio.com/</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr"/>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1bE1RAucGmIWyKiQf7msDKZSJsRaCeRj4K0U5NrSIaUI/edit?tab=t.0; Instagram: https://www.instagram.com/livssketch; Vimeo: https://vimeo.com/user135418221</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Xiaobei Song</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>xiaobeisong@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Experimental Animation (MFA 2) — Independent Filmmaking / 2D Animation / Visual Development, Background Design</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr"/>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>https://xiaobeisong.myportfolio.com/</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr"/>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1_fXdgz3O7sYmxUIByOUias0qxYZ_QqHKbcnKc11Kx3w/edit?usp=sharing; Instagram: https://www.instagram.com/bi_a_song/</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Haoyue Xu</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>haoyuexu@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Experimental Animation (MFA 2) — CG Animation / CG Modeling, Rigging, Texturing / Visual Development, Background Design</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>https://www.therookies.co/entries/39863</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr"/>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1pf5Ctqir9jU_dGQZDn2fagjhV3E3oxE061xG67o4KGs/edit?usp=sharing; Instagram: https://www.instagram.com/unaxu.art; Vimeo: https://vimeo.com/user208217948</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Nikko Zixuan</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>zixuanzhou@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Experimental Animation (MFA 2) — Experimental Techniques / Stop-Motion, Puppetry / Motion Design</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr"/>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>https://nikkozixuanzhou.art/</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr"/>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>Resume: https://drive.google.com/drive/folders/1KRNGr3MiHsNT1XPudlmmF9Lkv-P6rU6L?usp=sharing; Instagram: https://www.instagram.com/y_w_metheus/</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Madeline Babuka Black</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>madelinebabukablack@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Experimental Animation (MFA 3) — 2D Animation / Experimental Techniques / Independent Filmmaking</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>https://madelinebabukablack.com/</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr"/>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1jYOH6qsZJT4WuHkxQLtk9Dx1So3eAowIBwuYbjwZesA/edit?usp=sharing; Instagram: https://www.instagram.com/madelineb.b/; Vimeo: https://vimeo.com/madelinebb</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Sarah Hawkins</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>sarahhawkins@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Experimental Animation (MFA 3) — Experimental Techniques / Teaching, Education / Illustration, Comics</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr"/>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>https://sarrahkinz.wixsite.com/sarah-hawkins</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr"/>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1lIkmOLszsnsKFzJDN3oTqHAB7EuKoMDsk_O0noBTCWM/edit?usp=sharing; Instagram: https://www.instagram.com/sarrahkinzart/; Youtube: https://www.youtube.com/@sarrahkinz6858/videos</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Calleen Koh</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>calleenkoh@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Experimental Animation (MFA 3) — Independent Filmmaking / Writing for Animation / Stop-Motion, Puppetry</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr"/>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>https://calleenkoh.com/</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr"/>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>Resume: https://drive.google.com/file/d/1LzhaiqRQWU6uOt8t3EFNe1CO_0ut-6qY/view?usp=drive_link; Instagram: https://www.instagram.com/calleenkoh; Vimeo: https://vimeo.com/calleenkoh</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Yama Li</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>yamali@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Experimental Animation (MFA 3) — CG Animation / Motion Design / CG Modeling, Rigging, Texturing</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr"/>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>https://www.yamasihanli.com/</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr"/>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1T7J70_Qwa7n1FweZhhzazp8v-Aqx4uPMtSRzz_5sLDo/edit?usp=sharing</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Cirrus Marlo Sauma</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>cirrussauma@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Experimental Animation (MFA 3) — 2D Animation / Stop-Motion, Puppetry / Illustration, Comics</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr"/>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>https://cirrussauma.com/</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr"/>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1suEmQmbJm1KasZpJMul_zUtQLDye-SjI8yyYJkfmSYI/edit?usp=sharing; Instagram: https://www.instagram.com/cirrusmarlosauma; Vimeo: https://vimeo.com/saumamvmt</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Shiyu Tang</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>shiyutang@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Experimental Animation (MFA 3) — Stop-Motion, Puppetry / 2D Animation / Compositing</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr"/>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>https://shiyutang.art/</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr"/>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1FOITtZFyO3ZyWAUJquOamcyF_Yys1Swi/edit?usp=drivesdk&amp;ouid=100190825795146273791&amp;rtpof=true&amp;sd=true; Instagram: https://www.instagram.com/_shiyu_tang; LinkedIn: https://www.linkedin.com/in/shiyu-tang-animation?utm_source=share&amp;utm_campaign=share_via&amp;utm_content=profile&amp;utm_medium=ios_app</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Julián Vargas</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>julianvargas@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Experimental Animation (MFA 3) — 2D Animation / Character Design / Stop-Motion, Puppetry</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr"/>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>https://www.allaboutjulian.com/</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr"/>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1U7CasbCUn1uwsSg3PxTqZOmmKJw3LA_VjEvMvGrYXlA/edit?usp=sharing; Instagram: https://www.instagram.com/julianupclose/; Youtube: https://www.youtube.com/@julianvargas2096/videos</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Yasmine (Yuanying) Xu</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>yuanyingxu@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Experimental Animation (MFA 3) — Motion Design / Stop-Motion, Puppetry / 2D Animation</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr"/>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>http://www.yasminexu.com</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr"/>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1zPBI5HfW00euHZLq154HlHiEBM-_K5Zq/edit?usp=drive_link&amp;ouid=104358452467235519842&amp;rtpof=true&amp;sd=true; Instagram: https://www.instagram.com/yasminexyy614/</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Yuxin Yang</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>yuxinyang@students.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Experimental Animation (MFA 3) — Independent Filmmaking / Stop-Motion, Puppetry / 2D Animation</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr"/>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>https://yangyuxin.squarespace.com/</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr"/>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>Resume: https://drive.google.com/drive/folders/1v0POZ-nZwda36CSqaOYeYg78fhZ1Ma32?usp=sharing; Instagram: https://www.instagram.com/ayang_anima</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Mengtong Chen</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>mengtongchen@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Experimental Animation (Recent Alumni) — 2D Animation / Experimental Techniques / Independent Filmmaking</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>http://www.mncu404.com/</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr"/>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>Resume: https://drive.google.com/drive/folders/1lk8QdqlsfnatNg_OffEH-v0R2BMzl0wg</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Benjamin Crowell</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>pbenjamincrowell@gmail.com</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Experimental Animation (Recent Alumni) — Independent Filmmaking / Stop-Motion, Puppetry / Writing for Animation</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr"/>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>https://www.benjamincrowell.com</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr"/>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/190C7rZDGWIhdZopnxQYbDQXjBE4SZm1wbPD_tBFSirg/edit?tab=t.0; Vimeo: https://vimeo.com/benjamincrowell; Youtube: https://www.youtube.com/@benjamincrowell/videos</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Eaven Harrington</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>soups.on.eav@gmail.com</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Experimental Animation (Recent Alumni) — Experimental Techniques / Independent Filmmaking / Character Design</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr"/>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>https://soups-on-eav.mmm.page/home</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr"/>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1jY6BA5BJ9XnD8R10K2_5_TGyPezDieq6ra-VlTXQxyQ/edit?usp=sharing; Instagram: https://www.instagram.com/soups_on_eav/; Youtube: https://www.youtube.com/@soupy2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Terri Lam</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>terrilam523@gmail.com</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Experimental Animation (Recent Alumni) — Illustration, Comics / Experimental Techniques / Visual Development, Background Design</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr"/>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>https://terrilam523.wixsite.com/artworks</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr"/>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>Resume: https://docs.google.com/document/d/1OPXq-F1INeaZzr1-Plzf9X0jiD2SHtJc1iiQDp0PZCg/edit?usp=sharing; Instagram: https://www.instagram.com/terrilam_art/; LinkedIn: https://www.linkedin.com/in/terri-lam-6a6696227/</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Miranda Rosales</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>mirandarosales@alum.calarts.edu</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Experimental Animation (Recent Alumni) — 2D Animation / CG Animation / Stop-Motion, Puppetry</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr"/>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>https://mirandarosales.cargo.site/animation</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>CalArts (Animation)</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr"/>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>Resume: https://drive.google.com/file/d/1s2CyVR1R14BvYRT72QnhG-LrvZlgaa2o/view?usp=sharing; Instagram: https://www.instagram.com/flordenub3/; Vimeo: https://vimeo.com/user184865467</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A5:I256"/>
+  <dataValidations count="2">
+    <dataValidation sqref="G6:G256" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H6:H256" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"No response,Interested,Not interested,Bounced,Follow-up needed"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Dezi Art Prize Student Data Scraping/master_students.xlsx
+++ b/Dezi Art Prize Student Data Scraping/master_students.xlsx
@@ -79333,7 +79333,7 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Name only, from artwork photo caption credit on ICA exhibition page; likely incomplete relative to full graduating cohort</t>
+          <t>No email found via web search — LinkedIn, Pinterest, Facebook, and ethicaljewelry.org VCU chapter page all confirmed her identity (metal/glass artist, Craft/Material Studies MFA) but none published a direct email; no personal portfolio site found</t>
         </is>
       </c>
     </row>
@@ -79368,7 +79368,7 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Name only, from artwork photo caption credit on ICA exhibition page; likely incomplete relative to full graduating cohort</t>
+          <t>No email found — confirmed real via VCU Scholars Compass thesis record and VCUarts Sculpture Instagram feature; aneuscheler.info found but appears to be an unrelated site with no VCU/contact content; no personal portfolio site found</t>
         </is>
       </c>
     </row>
@@ -79378,7 +79378,11 @@
           <t>Aya Khalife</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>khalifehaya7@gmail.com</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>MFA Fine Arts</t>
@@ -79389,7 +79393,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://www.ayakhalife.com/</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>VCU</t>
@@ -79403,20 +79411,20 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Name only, from artwork photo caption credit on ICA exhibition page (collaborative piece, multiple credited artists); likely incomplete relative to full graduating cohort</t>
+          <t>Email confirmed by user (portfolio site ayakhalife.com, JS-rendered Readymag site, personal email surfaced via 'Reach out' mailto link only visible on hover — not captured by automated fetch/crawl4ai)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Suzy Slykin</t>
+          <t>Suzy Lykins</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MFA Fine Arts</t>
+          <t>MFA Painting and Printmaking</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -79438,7 +79446,7 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Name only, from artwork photo caption credit on ICA exhibition page (collaborative piece, multiple credited artists); likely incomplete relative to full graduating cohort</t>
+          <t>Name corrected from 'Suzy Slykin' (source ICA caption misspelling) to 'Suzy Lykins', confirmed via matching thesis title 'Post Opera' on VCU Scholars Compass (scholarscompass.vcu.edu/etd/7995/). No email found via web search — no personal site/social found under correct spelling</t>
         </is>
       </c>
     </row>
@@ -79448,10 +79456,14 @@
           <t>Rebecca Oh</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>rebeccaohart@gmail.com</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MFA Fine Arts</t>
+          <t>MFA Painting and Printmaking</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -79459,7 +79471,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>http://www.rebeccaoh.com/</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>VCU</t>
@@ -79473,7 +79489,7 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Name only, from artwork photo caption credit on ICA exhibition page (collaborative piece, multiple credited artists); likely incomplete relative to full graduating cohort</t>
+          <t>Email found via web search (own site rebeccaoh.com/about, verified in raw HTML: 'Feel free to e-mail the artist at rebeccaohart@gmail.com')</t>
         </is>
       </c>
     </row>
@@ -79483,10 +79499,14 @@
           <t>David Guarnizo</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>guarnizode@vcu.edu</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MFA Fine Arts</t>
+          <t>MFA Photography and Film</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -79494,7 +79514,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/david-guarnizo/</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>VCU</t>
@@ -79508,7 +79532,7 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Name only, from artwork photo caption credit on ICA exhibition page; likely incomplete relative to full graduating cohort</t>
+          <t>Email found via web search (VCU School of the Arts directory page, verified in raw HTML)</t>
         </is>
       </c>
     </row>
@@ -79518,10 +79542,14 @@
           <t>Tyna Ontko</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ontkotyna@gmail.com</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MFA Fine Arts</t>
+          <t>MFA Sculpture and Extended Media</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -79529,7 +79557,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://tynaontko.com/</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>VCU</t>
@@ -79543,7 +79575,7 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Name only, from artwork photo caption credit on ICA exhibition page; likely incomplete relative to full graduating cohort</t>
+          <t>Email found via web search (own site tynaontko.com/contact, address was obfuscated as 'ontkotyna(at)gmail(dot)com' in page text, deobfuscated)</t>
         </is>
       </c>
     </row>
@@ -79556,7 +79588,7 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MFA Fine Arts</t>
+          <t>MFA Painting and Printmaking</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -79578,7 +79610,7 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Name only, from artwork photo caption credit on ICA exhibition page; likely incomplete relative to full graduating cohort</t>
+          <t>No email found via web search — confirmed real (BFA 2021 UCF, painter) via ArtFields competition page and Instagram, but no personal portfolio site found and no email published anywhere</t>
         </is>
       </c>
     </row>
@@ -79591,7 +79623,7 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MFA Fine Arts</t>
+          <t>MFA Craft/Material Studies</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -79613,7 +79645,7 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Name only, from artwork photo caption credit on ICA exhibition page; likely incomplete relative to full graduating cohort</t>
+          <t>No email found via web search — confirmed real via MutualArt profile and LinkedIn (Textile Artist and Designer), but no personal portfolio site found and no email published anywhere</t>
         </is>
       </c>
     </row>
@@ -79626,7 +79658,7 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MFA Fine Arts</t>
+          <t>MFA Craft/Material Studies</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -79648,7 +79680,7 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Name only, from artwork photo caption credit on ICA exhibition page; likely incomplete relative to full graduating cohort</t>
+          <t>No email found via web search — confirmed real (BFA Ceramics, Indiana University Southeast 2020) via Alma's Gallery product page and Instagram (@brooklingrantzceramics), but no personal website found and no email published anywhere</t>
         </is>
       </c>
     </row>
@@ -79658,10 +79690,14 @@
           <t>Molly Garrett</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>hi@mollygarrett.com</t>
+        </is>
+      </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MFA Fine Arts</t>
+          <t>MFA Graphic Design</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -79669,7 +79705,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://mollygarrett.com/</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>VCU</t>
@@ -79683,7 +79723,7 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Name only, from artwork photo caption credit on ICA exhibition page; likely incomplete relative to full graduating cohort</t>
+          <t>Email found via web search (own site mollygarrett.com/contact, address was obfuscated as 'hi [at] mollygarrett.com' in page text, deobfuscated)</t>
         </is>
       </c>
     </row>
@@ -79696,7 +79736,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MFA Fine Arts</t>
+          <t>MFA Painting and Printmaking</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -79718,7 +79758,7 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Name only, from artwork photo caption credit on ICA exhibition page (collaborative piece, multiple credited artists); likely incomplete relative to full graduating cohort</t>
+          <t>No email found via web search — common name causes ambiguity (an unrelated NYC art historian also named Alex Bacon has a similar-looking alex-bacon.com site, confirmed NOT this person). Confirmed real via VCU Scholars Compass thesis 'Wiring Attachment' by Alexander Kunin Bacon and Bond Millen Gallery bio, but no personal site/email found for the correct person</t>
         </is>
       </c>
     </row>
@@ -79728,10 +79768,14 @@
           <t>Amy Duval</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>amys.duval@gmail.com</t>
+        </is>
+      </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MFA Fine Arts</t>
+          <t>MFA Craft/Material Studies</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -79739,7 +79783,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://www.duvalceramics.ca/</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>VCU</t>
@@ -79753,7 +79801,7 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Name only, from artwork photo caption credit on ICA exhibition page; likely incomplete relative to full graduating cohort</t>
+          <t>Email found via web search (own site duvalceramics.ca/contact, JS-rendered — found via interactive Playwright probe of the contact form page)</t>
         </is>
       </c>
     </row>

--- a/Dezi Art Prize Student Data Scraping/master_students.xlsx
+++ b/Dezi Art Prize Student Data Scraping/master_students.xlsx
@@ -14633,7 +14633,11 @@
           <t>Mandy Darrington</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mandylynndarrington@gmail.com</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>MFA Studio Art</t>
@@ -14646,7 +14650,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://art.osu.edu/events/mfa-thesis-exhibition-desire-lines</t>
+          <t>https://www.mandydarrington.com/</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -14662,7 +14666,7 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Name only, from 'Participating Artists' list; no email/portfolio published on source page</t>
+          <t>Email found via web search (own site mandydarrington.com/about, obfuscated as 'mandylynndarrington [at] gmail [dot] com', deobfuscated)</t>
         </is>
       </c>
     </row>
@@ -14685,7 +14689,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://art.osu.edu/events/mfa-thesis-exhibition-desire-lines</t>
+          <t>https://www.annelise-duque.com/</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -14701,7 +14705,7 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Name only, from 'Participating Artists' list; no email/portfolio published on source page</t>
+          <t>No email found — own site annelise-duque.com found (CV/contact pages checked directly and via interactive Playwright probe), only Squarespace placeholder text present, no personal email published</t>
         </is>
       </c>
     </row>
@@ -14711,7 +14715,11 @@
           <t>William Evans</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>evans_william@live.com</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>MFA Studio Art</t>
@@ -14724,7 +14732,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://art.osu.edu/events/mfa-thesis-exhibition-desire-lines</t>
+          <t>https://www.williamevans.studio/</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -14740,7 +14748,7 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Name only, from 'Participating Artists' list; no email/portfolio published on source page</t>
+          <t>Email found via web search (own site williamevans.studio/about, plain text)</t>
         </is>
       </c>
     </row>
@@ -14779,7 +14787,7 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Name only, from 'Participating Artists' list; no email/portfolio published on source page</t>
+          <t>No email found — confirmed real (ceramic artist, Bronx NY, BFA SUNY New Paltz) via Instagram and Clay Art Center residency mentions; OSU directory profile page 404s, no personal site found</t>
         </is>
       </c>
     </row>
@@ -14802,7 +14810,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://art.osu.edu/events/mfa-thesis-exhibition-desire-lines</t>
+          <t>https://www.josiahjamison.com/</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -14818,7 +14826,7 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Name only, from 'Participating Artists' list; no email/portfolio published on source page</t>
+          <t>No email found — own site josiahjamison.com found (about/CV pages checked), only Squarespace placeholder text present, no personal email published</t>
         </is>
       </c>
     </row>
@@ -14857,7 +14865,7 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Name only, from 'Participating Artists' list; no email/portfolio published on source page</t>
+          <t>No email found via web search — no personal site surfaced; note a 'Matthew Machado' also appears as an OSU Art Department Lecturer, possibly the same person post-graduation, but not confirmed as the same identity so not used</t>
         </is>
       </c>
     </row>
@@ -14867,7 +14875,11 @@
           <t>Andrew Mehall</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>mehall.11@osu.edu</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr">
         <is>
           <t>MFA Studio Art</t>
@@ -14880,7 +14892,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://art.osu.edu/events/mfa-thesis-exhibition-desire-lines</t>
+          <t>https://art.osu.edu/people/mehall.11</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -14896,7 +14908,7 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Name only, from 'Participating Artists' list; no email/portfolio published on source page</t>
+          <t>Email found via web search (OSU Department of Art directory profile, institutional address, verified in raw HTML)</t>
         </is>
       </c>
     </row>
@@ -14919,7 +14931,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://art.osu.edu/events/mfa-thesis-exhibition-desire-lines</t>
+          <t>https://livablefuturesnow.org/zazanaylor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -14935,7 +14947,7 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Name only, from 'Participating Artists' list; no email/portfolio published on source page</t>
+          <t>No email found — confirmed real (Zachary Naylor, b. 1993 Waterbury CT) via Livable Futures artist page, only Squarespace placeholder text present; OSU directory profile page 404s</t>
         </is>
       </c>
     </row>
@@ -14945,10 +14957,14 @@
           <t>Ivan David Ng</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>info@ivandavidng.com</t>
+        </is>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MFA Studio Art</t>
+          <t>MFA Drawing and Painting</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -14958,7 +14974,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://art.osu.edu/events/mfa-thesis-exhibition-desire-lines</t>
+          <t>https://www.ivandavidng.com/</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -14974,7 +14990,7 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Name only, from 'Participating Artists' list; no email/portfolio published on source page</t>
+          <t>Email found via web search (own site ivandavidng.com/about, plain text)</t>
         </is>
       </c>
     </row>
@@ -14987,7 +15003,7 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MFA Studio Art</t>
+          <t>MFA Art and Technology</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -14997,7 +15013,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://art.osu.edu/events/mfa-thesis-exhibition-desire-lines</t>
+          <t>http://www.julianrobbins.art/</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -15013,7 +15029,7 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Name only, from 'Participating Artists' list; no email/portfolio published on source page</t>
+          <t>No email found — own site julianrobbinsart.wordpress.com/julianrobbins.art found, checked via interactive Playwright probe, no email/contact affordance found; OSU directory profile page 404s</t>
         </is>
       </c>
     </row>
@@ -15036,7 +15052,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://art.osu.edu/events/mfa-thesis-exhibition-desire-lines</t>
+          <t>https://www.isabellasaraceni.com/</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -15052,7 +15068,7 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Name only, from 'Participating Artists' list; no email/portfolio published on source page</t>
+          <t>No email found — own site isabellasaraceni.com found, checked via interactive Playwright probe, no email/contact affordance found; OSU directory profile page 404s</t>
         </is>
       </c>
     </row>
@@ -15065,7 +15081,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MFA Studio Art</t>
+          <t>MFA Studio Art (Ceramics)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -15075,7 +15091,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://art.osu.edu/events/mfa-thesis-exhibition-desire-lines</t>
+          <t>https://www.alextrippe.com/</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -15091,7 +15107,7 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Name only, from 'Participating Artists' list; no email/portfolio published on source page</t>
+          <t>No email found — own site alextrippe.com found (full name Alexandra Trippe), checked via interactive Playwright probe, no email/contact affordance found; OSU directory profile page 404s</t>
         </is>
       </c>
     </row>
@@ -15130,7 +15146,7 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Name only, from 'Participating Artists' list; no email/portfolio published on source page</t>
+          <t>No email found via web search — confirmed real via First-Year MFA Show and Desire Lines exhibition mentions, but no personal site found and no email published anywhere</t>
         </is>
       </c>
     </row>
